--- a/research/traditional_assets/database/data/poland/poland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.147</v>
+        <v>0.029425</v>
       </c>
       <c r="E2">
-        <v>0.0573</v>
+        <v>-0.10285</v>
       </c>
       <c r="G2">
-        <v>0.246615753169214</v>
+        <v>0.8830614346944877</v>
       </c>
       <c r="H2">
-        <v>0.241676718330539</v>
+        <v>0.867146227198724</v>
       </c>
       <c r="I2">
-        <v>0.4858565529568691</v>
+        <v>0.0502209522543775</v>
       </c>
       <c r="J2">
-        <v>0.4516394336797713</v>
+        <v>0.04797711511143676</v>
       </c>
       <c r="K2">
-        <v>150.532</v>
+        <v>-14.057</v>
       </c>
       <c r="L2">
-        <v>0.5057706070309009</v>
+        <v>-0.1167641293152141</v>
       </c>
       <c r="M2">
-        <v>25.4834</v>
+        <v>28.6244</v>
       </c>
       <c r="N2">
-        <v>0.03951159761845695</v>
+        <v>0.05686654309729995</v>
       </c>
       <c r="O2">
-        <v>0.1692889219567932</v>
+        <v>-2.036309312086505</v>
       </c>
       <c r="P2">
-        <v>16.8734</v>
+        <v>17.6464</v>
       </c>
       <c r="Q2">
-        <v>0.02616193252294716</v>
+        <v>0.03505714586549216</v>
       </c>
       <c r="R2">
-        <v>0.112091781149523</v>
+        <v>-1.255346090915558</v>
       </c>
       <c r="S2">
-        <v>8.609999999999999</v>
+        <v>10.978</v>
       </c>
       <c r="T2">
-        <v>0.3378670036180415</v>
+        <v>0.3835189558558432</v>
       </c>
       <c r="U2">
-        <v>66.586</v>
+        <v>60.635</v>
       </c>
       <c r="V2">
-        <v>0.1032405110394443</v>
+        <v>0.120460266091334</v>
       </c>
       <c r="W2">
-        <v>0.07231363424848766</v>
+        <v>-0.02689985795454546</v>
       </c>
       <c r="X2">
-        <v>0.05041519074416259</v>
+        <v>0.08144168498810182</v>
       </c>
       <c r="Y2">
-        <v>0.02189844350432507</v>
+        <v>-0.1083415429426473</v>
       </c>
       <c r="Z2">
-        <v>0.5029929898802804</v>
+        <v>0.1665345600573246</v>
       </c>
       <c r="AA2">
-        <v>-0.02114801466141718</v>
+        <v>-0.04480633892730559</v>
       </c>
       <c r="AB2">
-        <v>0.05010649067802009</v>
+        <v>0.08088425061648849</v>
       </c>
       <c r="AC2">
-        <v>-0.07141283994918698</v>
+        <v>-0.1256265657892554</v>
       </c>
       <c r="AD2">
-        <v>136.337</v>
+        <v>113.389</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>136.337</v>
+        <v>113.389</v>
       </c>
       <c r="AG2">
-        <v>69.75099999999999</v>
+        <v>52.754</v>
       </c>
       <c r="AH2">
-        <v>0.1745008620281404</v>
+        <v>0.1838492095662748</v>
       </c>
       <c r="AI2">
-        <v>0.1665188800461192</v>
+        <v>0.1765636508309729</v>
       </c>
       <c r="AJ2">
-        <v>0.09759329295337554</v>
+        <v>0.09486167429398595</v>
       </c>
       <c r="AK2">
-        <v>0.0927340120878215</v>
+        <v>0.09071056667881781</v>
       </c>
       <c r="AL2">
-        <v>6.639</v>
+        <v>8.357999999999999</v>
       </c>
       <c r="AM2">
-        <v>5.601</v>
+        <v>5.595999999999998</v>
       </c>
       <c r="AN2">
-        <v>0.9269833283472491</v>
+        <v>11.5868587778459</v>
       </c>
       <c r="AO2">
-        <v>21.78114173821359</v>
+        <v>0.7233787987556832</v>
       </c>
       <c r="AP2">
-        <v>0.4742514074356115</v>
+        <v>5.390762313509095</v>
       </c>
       <c r="AQ2">
-        <v>25.81771112301375</v>
+        <v>1.080414581844175</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Skarbiec Holding S.A. (WSE:SKH)</t>
+          <t>Unfold.vc ASI S.A. (WSE:UNF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.139</v>
-      </c>
-      <c r="E3">
-        <v>0.208</v>
+        <v>1.124</v>
       </c>
       <c r="G3">
-        <v>0.5203045685279188</v>
+        <v>1.423312883435583</v>
       </c>
       <c r="H3">
-        <v>0.5203045685279188</v>
+        <v>1.423312883435583</v>
       </c>
       <c r="I3">
-        <v>0.4035532994923858</v>
+        <v>0.9325153374233128</v>
       </c>
       <c r="J3">
-        <v>0.3223285589576126</v>
+        <v>0.9325153374233128</v>
       </c>
       <c r="K3">
-        <v>12.5</v>
+        <v>5.37</v>
       </c>
       <c r="L3">
-        <v>0.317258883248731</v>
+        <v>0.6588957055214724</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.663</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03745762711864407</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.123463687150838</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.663</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03745762711864407</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.123463687150838</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>34.6</v>
+        <v>2.15</v>
       </c>
       <c r="V3">
-        <v>0.6837944664031621</v>
+        <v>0.1214689265536723</v>
       </c>
       <c r="W3">
-        <v>0.314070351758794</v>
+        <v>0.3420382165605096</v>
       </c>
       <c r="X3">
-        <v>0.05044813707461854</v>
+        <v>0.08082114696334053</v>
       </c>
       <c r="Y3">
-        <v>0.2636222146841755</v>
+        <v>0.2612170695971691</v>
       </c>
       <c r="Z3">
-        <v>8.834080717488797</v>
+        <v>0.5892986261749821</v>
       </c>
       <c r="AA3">
-        <v>2.847476507383397</v>
+        <v>0.549530007230658</v>
       </c>
       <c r="AB3">
-        <v>0.04996290898807608</v>
+        <v>0.08077553554787026</v>
       </c>
       <c r="AC3">
-        <v>2.797513598395321</v>
+        <v>0.4687544716827878</v>
       </c>
       <c r="AD3">
-        <v>0.974</v>
+        <v>0.029</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.974</v>
+        <v>0.029</v>
       </c>
       <c r="AG3">
-        <v>-33.626</v>
+        <v>-2.121</v>
       </c>
       <c r="AH3">
-        <v>0.0188854849342692</v>
+        <v>0.001635738056291951</v>
       </c>
       <c r="AI3">
-        <v>0.0186683022194963</v>
+        <v>0.001673495296901148</v>
       </c>
       <c r="AJ3">
-        <v>-1.981029810298104</v>
+        <v>-0.1361448103215868</v>
       </c>
       <c r="AK3">
-        <v>-1.913394787754638</v>
+        <v>-0.1397325251992885</v>
       </c>
       <c r="AL3">
-        <v>0.023</v>
+        <v>0.062</v>
       </c>
       <c r="AM3">
-        <v>0.011</v>
+        <v>-0.192</v>
       </c>
       <c r="AN3">
-        <v>0.06049689440993788</v>
+        <v>0.003810775295663601</v>
       </c>
       <c r="AO3">
-        <v>691.304347826087</v>
+        <v>122.5806451612903</v>
       </c>
       <c r="AP3">
-        <v>-2.088571428571429</v>
+        <v>-0.2787122207621551</v>
       </c>
       <c r="AQ3">
-        <v>1445.454545454545</v>
+        <v>-39.58333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -852,35 +852,32 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0122</v>
-      </c>
       <c r="G4">
-        <v>-0.03951890034364262</v>
+        <v>0.1611650485436893</v>
       </c>
       <c r="H4">
-        <v>-0.03951890034364262</v>
+        <v>0.1611650485436893</v>
       </c>
       <c r="I4">
-        <v>0.1993127147766323</v>
+        <v>0.08058252427184466</v>
       </c>
       <c r="J4">
-        <v>0.1907216494845361</v>
+        <v>0.07363575493806496</v>
       </c>
       <c r="K4">
-        <v>0.11</v>
+        <v>0.053</v>
       </c>
       <c r="L4">
-        <v>0.1890034364261169</v>
+        <v>0.05145631067961165</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.002</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.001098901098901099</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.03773584905660377</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -892,73 +889,73 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0.008</v>
+        <v>0.089</v>
       </c>
       <c r="V4">
-        <v>0.003686635944700461</v>
+        <v>0.04890109890109889</v>
       </c>
       <c r="W4">
-        <v>0.7096774193548387</v>
+        <v>0.2030651340996169</v>
       </c>
       <c r="X4">
-        <v>0.05017829068773309</v>
+        <v>0.08089619235639051</v>
       </c>
       <c r="Y4">
-        <v>0.6594991286671057</v>
+        <v>0.1221689417432263</v>
       </c>
       <c r="Z4">
-        <v>4.73170731707317</v>
+        <v>3.759124087591241</v>
       </c>
       <c r="AA4">
-        <v>0.9024390243902439</v>
+        <v>0.2768059400956456</v>
       </c>
       <c r="AB4">
-        <v>0.05047432829536568</v>
+        <v>0.08078906841646831</v>
       </c>
       <c r="AC4">
-        <v>0.8519646960948782</v>
+        <v>0.1960168716791773</v>
       </c>
       <c r="AD4">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.021</v>
+        <v>0.007</v>
       </c>
       <c r="AG4">
-        <v>0.013</v>
+        <v>-0.08199999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.009584664536741215</v>
+        <v>0.003831417624521073</v>
       </c>
       <c r="AI4">
-        <v>0.07446808510638298</v>
+        <v>0.02966101694915254</v>
       </c>
       <c r="AJ4">
-        <v>0.005955107650022906</v>
+        <v>-0.04718066743383199</v>
       </c>
       <c r="AK4">
-        <v>0.04744525547445255</v>
+        <v>-0.5578231292517005</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.1810344827586207</v>
+        <v>0.07865168539325844</v>
       </c>
       <c r="AP4">
-        <v>0.1120689655172414</v>
-      </c>
-      <c r="AQ4">
-        <v>-38.66666666666666</v>
+        <v>-0.9213483146067415</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dr.Finance S.A. (WSE:DRF)</t>
+          <t>Quercus TFI S.A. (WSE:QRS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,37 +975,37 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.14</v>
+        <v>-0.00625</v>
       </c>
       <c r="E5">
-        <v>0.0573</v>
+        <v>-0.0607</v>
       </c>
       <c r="G5">
-        <v>0.0007575757575757576</v>
+        <v>0.3136563876651983</v>
       </c>
       <c r="H5">
-        <v>0.0007575757575757576</v>
+        <v>0.3136563876651983</v>
       </c>
       <c r="I5">
-        <v>0.01818181818181818</v>
+        <v>0.2356828193832599</v>
       </c>
       <c r="J5">
-        <v>0.01636363636363636</v>
+        <v>0.193499851710394</v>
       </c>
       <c r="K5">
-        <v>0.036</v>
+        <v>4.93</v>
       </c>
       <c r="L5">
-        <v>0.01363636363636363</v>
+        <v>0.2171806167400881</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>4.57</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.1106537530266344</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.9269776876267749</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1020,73 +1017,79 @@
         <v>-0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>4.57</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0.159</v>
+        <v>15.1</v>
       </c>
       <c r="V5">
-        <v>0.1445454545454545</v>
+        <v>0.3656174334140436</v>
       </c>
       <c r="W5">
-        <v>0.1988950276243094</v>
+        <v>0.2581151832460732</v>
       </c>
       <c r="X5">
-        <v>0.04995671973678575</v>
+        <v>0.08099755428631714</v>
       </c>
       <c r="Y5">
-        <v>0.1489383078875236</v>
+        <v>0.1771176289597561</v>
       </c>
       <c r="Z5">
-        <v>46.31578947368422</v>
+        <v>1.374008837237455</v>
       </c>
       <c r="AA5">
-        <v>0.7578947368421054</v>
+        <v>0.2658705062542185</v>
       </c>
       <c r="AB5">
-        <v>0.04993050393175152</v>
+        <v>0.08076495474107177</v>
       </c>
       <c r="AC5">
-        <v>0.7079642329103539</v>
+        <v>0.1851055515131468</v>
       </c>
       <c r="AD5">
-        <v>0.002</v>
+        <v>0.282</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.002</v>
+        <v>0.282</v>
       </c>
       <c r="AG5">
-        <v>-0.157</v>
+        <v>-14.818</v>
       </c>
       <c r="AH5">
-        <v>0.001814882032667877</v>
+        <v>0.00678178057813477</v>
       </c>
       <c r="AI5">
-        <v>0.009049773755656109</v>
+        <v>0.01660581792486162</v>
       </c>
       <c r="AJ5">
-        <v>-0.1664899257688229</v>
+        <v>-0.559549882939355</v>
       </c>
       <c r="AK5">
-        <v>-2.532258064516129</v>
+        <v>-7.87353878852285</v>
       </c>
       <c r="AL5">
-        <v>0.001</v>
+        <v>0.027</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-0.293</v>
       </c>
       <c r="AN5">
-        <v>0.03921568627450981</v>
+        <v>0.04723618090452261</v>
       </c>
       <c r="AO5">
-        <v>48</v>
+        <v>198.1481481481481</v>
       </c>
       <c r="AP5">
-        <v>-3.07843137254902</v>
+        <v>-2.482077051926298</v>
+      </c>
+      <c r="AQ5">
+        <v>-18.25938566552901</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Venture INC ASI S.A. (WSE:VTI)</t>
+          <t>Erato Energy S.A. (WSE:ERA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,121 +1109,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>1.238</v>
       </c>
       <c r="E6">
-        <v>0.328</v>
+        <v>-0.229</v>
       </c>
       <c r="G6">
-        <v>0.5969498910675382</v>
+        <v>0.07361111111111111</v>
       </c>
       <c r="H6">
-        <v>0.5969498910675382</v>
+        <v>0.07361111111111111</v>
       </c>
       <c r="I6">
-        <v>0.9063180827886711</v>
+        <v>0.02759259259259259</v>
       </c>
       <c r="J6">
-        <v>0.9013581330818674</v>
+        <v>0.01379629629629629</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>0.192</v>
       </c>
       <c r="L6">
-        <v>0.8714596949891068</v>
+        <v>0.008888888888888889</v>
       </c>
       <c r="M6">
-        <v>0.526</v>
+        <v>0.081</v>
       </c>
       <c r="N6">
-        <v>0.02565853658536586</v>
+        <v>0.004402173913043479</v>
       </c>
       <c r="O6">
-        <v>0.1315</v>
+        <v>0.421875</v>
       </c>
       <c r="P6">
-        <v>0.526</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02565853658536586</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1315</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>1.87</v>
+        <v>0.183</v>
       </c>
       <c r="V6">
-        <v>0.09121951219512196</v>
+        <v>0.009945652173913045</v>
       </c>
       <c r="W6">
-        <v>0.3174603174603174</v>
+        <v>0.006736842105263158</v>
       </c>
       <c r="X6">
-        <v>0.04990546078544718</v>
+        <v>0.08401686420629012</v>
       </c>
       <c r="Y6">
-        <v>0.2675548566748703</v>
+        <v>-0.07728002210102697</v>
       </c>
       <c r="Z6">
-        <v>0.5438388625592417</v>
+        <v>8.473911337779523</v>
       </c>
       <c r="AA6">
-        <v>0.4901935818537644</v>
+        <v>0.1169085916045508</v>
       </c>
       <c r="AB6">
-        <v>0.04990546078544718</v>
+        <v>0.0813035291121193</v>
       </c>
       <c r="AC6">
-        <v>0.4402881210683172</v>
+        <v>0.03560506249243152</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG6">
-        <v>-1.87</v>
+        <v>1.577</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.0873015873015873</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.4433249370277079</v>
       </c>
       <c r="AJ6">
-        <v>-0.1003757380568975</v>
+        <v>0.07894078189918408</v>
       </c>
       <c r="AK6">
-        <v>-0.1352133044107014</v>
+        <v>0.4164246105096382</v>
       </c>
       <c r="AL6">
-        <v>0.093</v>
+        <v>0.059</v>
       </c>
       <c r="AM6">
-        <v>0.093</v>
+        <v>0.059</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.257142857142857</v>
       </c>
       <c r="AO6">
-        <v>44.73118279569893</v>
+        <v>10.10169491525424</v>
       </c>
       <c r="AP6">
-        <v>-0.4495192307692308</v>
+        <v>1.126428571428572</v>
       </c>
       <c r="AQ6">
-        <v>44.73118279569893</v>
+        <v>10.10169491525424</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quercus TFI S.A. (WSE:QRS)</t>
+          <t>ALTUS SA (WSE:ALI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,118 +1243,121 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.06860000000000001</v>
+        <v>-0.341</v>
       </c>
       <c r="E7">
-        <v>-0.0669</v>
+        <v>-0.468</v>
       </c>
       <c r="G7">
-        <v>0.2737142857142857</v>
+        <v>0.3644444444444444</v>
       </c>
       <c r="H7">
-        <v>0.2737142857142857</v>
+        <v>0.3644444444444444</v>
       </c>
       <c r="I7">
-        <v>0.3057142857142857</v>
+        <v>0.1966666666666667</v>
       </c>
       <c r="J7">
-        <v>0.2522977490528193</v>
+        <v>0.1508282051282051</v>
       </c>
       <c r="K7">
-        <v>5.29</v>
+        <v>0.847</v>
       </c>
       <c r="L7">
-        <v>0.3022857142857143</v>
+        <v>0.0941111111111111</v>
       </c>
       <c r="M7">
-        <v>8.802399999999999</v>
+        <v>0.269</v>
       </c>
       <c r="N7">
-        <v>0.1479394957983193</v>
+        <v>0.01805369127516778</v>
       </c>
       <c r="O7">
-        <v>1.663969754253308</v>
+        <v>0.3175914994096812</v>
       </c>
       <c r="P7">
-        <v>4.2924</v>
+        <v>0.269</v>
       </c>
       <c r="Q7">
-        <v>0.07214117647058824</v>
+        <v>0.01805369127516778</v>
       </c>
       <c r="R7">
-        <v>0.8114177693761814</v>
+        <v>0.3175914994096812</v>
       </c>
       <c r="S7">
-        <v>4.509999999999999</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.5123602653821685</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>3.01</v>
+        <v>2.46</v>
       </c>
       <c r="V7">
-        <v>0.05058823529411764</v>
+        <v>0.1651006711409396</v>
       </c>
       <c r="W7">
-        <v>0.2922651933701657</v>
+        <v>0.03184210526315789</v>
       </c>
       <c r="X7">
-        <v>0.05011015199280926</v>
+        <v>0.0809342732434282</v>
       </c>
       <c r="Y7">
-        <v>0.2421550413773564</v>
+        <v>-0.0490921679802703</v>
       </c>
       <c r="Z7">
-        <v>1.566696508504924</v>
+        <v>0.3560830860534124</v>
       </c>
       <c r="AA7">
-        <v>0.3952740025447033</v>
+        <v>0.05370737274594841</v>
       </c>
       <c r="AB7">
-        <v>0.04995434918671586</v>
+        <v>0.08079591276785066</v>
       </c>
       <c r="AC7">
-        <v>0.3453196533579874</v>
+        <v>-0.02708854002190225</v>
       </c>
       <c r="AD7">
-        <v>0.432</v>
+        <v>0.074</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.432</v>
+        <v>0.074</v>
       </c>
       <c r="AG7">
-        <v>-2.578</v>
+        <v>-2.386</v>
       </c>
       <c r="AH7">
-        <v>0.007208169258492958</v>
+        <v>0.004941899292106317</v>
       </c>
       <c r="AI7">
-        <v>0.02211755068605365</v>
+        <v>0.002999108373186349</v>
       </c>
       <c r="AJ7">
-        <v>-0.04529004602789782</v>
+        <v>-0.1906664535719994</v>
       </c>
       <c r="AK7">
-        <v>-0.1560343784045515</v>
+        <v>-0.1074097416043936</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AM7">
-        <v>-0.002</v>
+        <v>-0.141</v>
       </c>
       <c r="AN7">
-        <v>0.07840290381125227</v>
+        <v>0.04065934065934065</v>
+      </c>
+      <c r="AO7">
+        <v>65.55555555555556</v>
       </c>
       <c r="AP7">
-        <v>-0.4678765880217786</v>
+        <v>-1.310989010989011</v>
       </c>
       <c r="AQ7">
-        <v>-2675</v>
+        <v>-12.5531914893617</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MCI Capital Alternatywna Spólka Inwestycyjna S.A. (WSE:MCI)</t>
+          <t>Starhedge S.A. (WSE:SHG)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1370,116 +1376,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D8">
+        <v>1.485</v>
+      </c>
+      <c r="E8">
+        <v>0.00045</v>
+      </c>
       <c r="G8">
-        <v>0.3291044776119403</v>
+        <v>0.1237864077669903</v>
       </c>
       <c r="H8">
-        <v>0.3291044776119403</v>
+        <v>0.1237864077669903</v>
       </c>
       <c r="I8">
-        <v>0.9761194029850747</v>
+        <v>0.07487864077669902</v>
       </c>
       <c r="J8">
-        <v>0.9761194029850747</v>
+        <v>0.07487864077669902</v>
       </c>
       <c r="K8">
-        <v>152.4</v>
+        <v>0.509</v>
       </c>
       <c r="L8">
-        <v>1.137313432835821</v>
+        <v>0.06177184466019418</v>
       </c>
       <c r="M8">
-        <v>9.41</v>
+        <v>0.029</v>
       </c>
       <c r="N8">
-        <v>0.03563044301400984</v>
+        <v>0.003629536921151439</v>
       </c>
       <c r="O8">
-        <v>0.06174540682414698</v>
+        <v>0.05697445972495089</v>
       </c>
       <c r="P8">
-        <v>7</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.02650511170011359</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.04593175853018373</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>2.41</v>
+        <v>0.029</v>
       </c>
       <c r="T8">
-        <v>0.2561105207226355</v>
+        <v>1</v>
       </c>
       <c r="U8">
-        <v>5.45</v>
+        <v>0.127</v>
       </c>
       <c r="V8">
-        <v>0.02063612268080273</v>
+        <v>0.01589486858573216</v>
       </c>
       <c r="W8">
-        <v>0.4565608148591971</v>
+        <v>0.04669724770642202</v>
       </c>
       <c r="X8">
-        <v>0.05571260892649202</v>
+        <v>0.08638115635932486</v>
       </c>
       <c r="Y8">
-        <v>0.4008482059327051</v>
+        <v>-0.03968390865290285</v>
       </c>
       <c r="Z8">
-        <v>0.3609952693455749</v>
+        <v>0.6163051608077785</v>
       </c>
       <c r="AA8">
-        <v>0.3523744867940388</v>
+        <v>0.04614809274495138</v>
       </c>
       <c r="AB8">
-        <v>0.05042502324928605</v>
+        <v>0.08163932045536477</v>
       </c>
       <c r="AC8">
-        <v>0.3019494635447527</v>
+        <v>-0.03549122771041339</v>
       </c>
       <c r="AD8">
-        <v>54.4</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>54.4</v>
+        <v>1.32</v>
       </c>
       <c r="AG8">
-        <v>48.95</v>
+        <v>1.193</v>
       </c>
       <c r="AH8">
-        <v>0.1708006279434851</v>
+        <v>0.1417830290010741</v>
       </c>
       <c r="AI8">
-        <v>0.1058159891071776</v>
+        <v>0.09482758620689656</v>
       </c>
       <c r="AJ8">
-        <v>0.1563647979555981</v>
+        <v>0.1299139714690188</v>
       </c>
       <c r="AK8">
-        <v>0.09623513221271994</v>
+        <v>0.08649314869861525</v>
       </c>
       <c r="AL8">
-        <v>2.12</v>
+        <v>0.206</v>
       </c>
       <c r="AM8">
-        <v>2.12</v>
+        <v>0.143</v>
       </c>
       <c r="AN8">
-        <v>0.4152671755725191</v>
+        <v>1.517241379310345</v>
       </c>
       <c r="AO8">
-        <v>61.69811320754717</v>
+        <v>2.995145631067961</v>
       </c>
       <c r="AP8">
-        <v>0.3736641221374046</v>
+        <v>1.371264367816092</v>
       </c>
       <c r="AQ8">
-        <v>61.69811320754717</v>
+        <v>4.314685314685315</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1502,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Invista S.A. (WSE:INV)</t>
+          <t>Nexity Global S.A. (WSE:NXG)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1499,28 +1511,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.539</v>
-      </c>
-      <c r="E9">
-        <v>0.0698</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="G9">
-        <v>45.16129032258064</v>
+        <v>-13.75</v>
       </c>
       <c r="H9">
-        <v>45.16129032258064</v>
+        <v>-13.75</v>
       </c>
       <c r="I9">
-        <v>38.70967741935484</v>
+        <v>0.4625</v>
       </c>
       <c r="J9">
-        <v>38.70967741935484</v>
+        <v>0.4625</v>
       </c>
       <c r="K9">
-        <v>1.24</v>
+        <v>-0.098</v>
       </c>
       <c r="L9">
-        <v>40</v>
+        <v>-1.225</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1529,7 +1538,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1538,79 +1547,79 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.01095238095238095</v>
+      </c>
+      <c r="W9">
+        <v>-0.8448275862068966</v>
+      </c>
+      <c r="X9">
+        <v>0.08139673415401688</v>
+      </c>
+      <c r="Y9">
+        <v>-0.9262243203609135</v>
+      </c>
+      <c r="Z9">
+        <v>0.07662835249042145</v>
+      </c>
+      <c r="AA9">
+        <v>0.03544061302681992</v>
+      </c>
+      <c r="AB9">
+        <v>0.08093395074374317</v>
+      </c>
+      <c r="AC9">
+        <v>-0.04549333771692325</v>
+      </c>
+      <c r="AD9">
+        <v>0.117</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0.117</v>
+      </c>
+      <c r="AG9">
+        <v>0.048</v>
+      </c>
+      <c r="AH9">
+        <v>0.0182328190743338</v>
+      </c>
+      <c r="AI9">
+        <v>-23.40000000000004</v>
+      </c>
+      <c r="AJ9">
+        <v>0.007561436672967864</v>
+      </c>
+      <c r="AK9">
+        <v>-0.6486486486486487</v>
+      </c>
+      <c r="AL9">
         <v>0.038</v>
       </c>
-      <c r="V9">
-        <v>0.001909547738693467</v>
-      </c>
-      <c r="W9">
-        <v>0.3815384615384615</v>
-      </c>
-      <c r="X9">
-        <v>0.05024688661458925</v>
-      </c>
-      <c r="Y9">
-        <v>0.3312915749238723</v>
-      </c>
-      <c r="Z9">
-        <v>0.007732601646295833</v>
-      </c>
-      <c r="AA9">
-        <v>0.2993265153404839</v>
-      </c>
-      <c r="AB9">
-        <v>0.05007057197361553</v>
-      </c>
-      <c r="AC9">
-        <v>0.2492559433668683</v>
-      </c>
-      <c r="AD9">
-        <v>0.241</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0.241</v>
-      </c>
-      <c r="AG9">
-        <v>0.203</v>
-      </c>
-      <c r="AH9">
-        <v>0.01196564222233256</v>
-      </c>
-      <c r="AI9">
-        <v>0.05862320603259548</v>
-      </c>
-      <c r="AJ9">
-        <v>0.01009799532408098</v>
-      </c>
-      <c r="AK9">
-        <v>0.04984041247237907</v>
-      </c>
-      <c r="AL9">
-        <v>0.052</v>
-      </c>
       <c r="AM9">
-        <v>0.052</v>
+        <v>-0.059</v>
       </c>
       <c r="AN9">
-        <v>0.2008333333333333</v>
+        <v>1.647887323943662</v>
       </c>
       <c r="AO9">
-        <v>23.07692307692308</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="AP9">
-        <v>0.1691666666666667</v>
+        <v>0.6760563380281691</v>
       </c>
       <c r="AQ9">
-        <v>23.07692307692308</v>
+        <v>-0.6271186440677965</v>
       </c>
     </row>
     <row r="10">
@@ -1621,7 +1630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALTUS SA (WSE:ALI)</t>
+          <t>MCI Capital Alternatywna Spólka Inwestycyjna S.A. (WSE:MCI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,118 +1639,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.292</v>
+        <v>-0.009889999999999999</v>
       </c>
       <c r="E10">
-        <v>-0.357</v>
+        <v>-0.145</v>
       </c>
       <c r="G10">
-        <v>0.2388157894736842</v>
+        <v>8.567307692307692</v>
       </c>
       <c r="H10">
-        <v>0.2388157894736842</v>
+        <v>8.567307692307692</v>
       </c>
       <c r="I10">
-        <v>0.2335526315789474</v>
+        <v>0.07134615384615384</v>
       </c>
       <c r="J10">
-        <v>0.1788859167148641</v>
+        <v>0.07134615384615384</v>
       </c>
       <c r="K10">
-        <v>2.38</v>
+        <v>3.69</v>
       </c>
       <c r="L10">
-        <v>0.156578947368421</v>
+        <v>0.3548076923076923</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>7.550499999999999</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.04011955366631243</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>2.04620596205962</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>7.261499999999999</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.03858395324123273</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>1.967886178861788</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>0.2889999999999997</v>
+      </c>
+      <c r="T10">
+        <v>0.03827561088669621</v>
       </c>
       <c r="U10">
-        <v>1.61</v>
+        <v>7.77</v>
       </c>
       <c r="V10">
-        <v>0.1087837837837838</v>
+        <v>0.04128586609989373</v>
       </c>
       <c r="W10">
-        <v>0.09558232931726908</v>
+        <v>0.008026974113552316</v>
       </c>
       <c r="X10">
-        <v>0.05044835542209045</v>
+        <v>0.08957953703056024</v>
       </c>
       <c r="Y10">
-        <v>0.04513397389517863</v>
+        <v>-0.08155256291700792</v>
       </c>
       <c r="Z10">
-        <v>0.8392689525702612</v>
+        <v>0.02044627936695173</v>
       </c>
       <c r="AA10">
-        <v>0.150133395950855</v>
+        <v>0.001458763393295979</v>
       </c>
       <c r="AB10">
-        <v>0.05003359951236469</v>
+        <v>0.08075030066726693</v>
       </c>
       <c r="AC10">
-        <v>0.1000997964384903</v>
+        <v>-0.07929153727397095</v>
       </c>
       <c r="AD10">
-        <v>0.285</v>
+        <v>48.8</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.285</v>
+        <v>48.8</v>
       </c>
       <c r="AG10">
-        <v>-1.325</v>
+        <v>41.03</v>
       </c>
       <c r="AH10">
-        <v>0.0188929400066291</v>
+        <v>0.2059071729957806</v>
       </c>
       <c r="AI10">
-        <v>0.009473159381751703</v>
+        <v>0.1164677804295943</v>
       </c>
       <c r="AJ10">
-        <v>-0.09833024118738405</v>
+        <v>0.1789905335252803</v>
       </c>
       <c r="AK10">
-        <v>-0.04653204565408253</v>
+        <v>0.09977384918415486</v>
       </c>
       <c r="AL10">
-        <v>0.039</v>
+        <v>4.35</v>
       </c>
       <c r="AM10">
-        <v>-0.034</v>
+        <v>4.188</v>
       </c>
       <c r="AN10">
-        <v>0.07894736842105263</v>
+        <v>57.68321513002364</v>
       </c>
       <c r="AO10">
-        <v>91.02564102564102</v>
+        <v>0.1705747126436782</v>
       </c>
       <c r="AP10">
-        <v>-0.3670360110803325</v>
+        <v>48.49881796690308</v>
       </c>
       <c r="AQ10">
-        <v>-104.4117647058824</v>
+        <v>0.1771728748806113</v>
       </c>
     </row>
     <row r="11">
@@ -1752,7 +1764,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital Partners S.A. (WSE:CPA)</t>
+          <t>Caspar Asset Management S.A. (WSE:CSR)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1761,118 +1773,112 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.245</v>
+        <v>0.25</v>
       </c>
       <c r="E11">
-        <v>-0.238</v>
+        <v>0.234</v>
       </c>
       <c r="G11">
-        <v>-0.1920212765957447</v>
+        <v>0.0001358695652173913</v>
       </c>
       <c r="H11">
-        <v>-0.1920212765957447</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0.6329787234042553</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.5175531914893617</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="L11">
-        <v>0.5957446808510639</v>
+        <v>0.1385869565217391</v>
       </c>
       <c r="M11">
-        <v>1.69</v>
+        <v>1.35</v>
       </c>
       <c r="N11">
-        <v>0.2456395348837209</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="O11">
-        <v>1.508928571428571</v>
+        <v>1.323529411764706</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>1.35</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>1.323529411764706</v>
       </c>
       <c r="S11">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>0.5570000000000001</v>
+        <v>1.44</v>
       </c>
       <c r="V11">
-        <v>0.08095930232558141</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="W11">
-        <v>0.1434058898847631</v>
+        <v>0.166394779771615</v>
       </c>
       <c r="X11">
-        <v>0.04990546078544718</v>
+        <v>0.08196146926123379</v>
       </c>
       <c r="Y11">
-        <v>0.09350042909931595</v>
+        <v>0.08443331051038122</v>
       </c>
       <c r="Z11">
-        <v>0.2727404613375888</v>
+        <v>1.84971098265896</v>
       </c>
       <c r="AA11">
-        <v>0.14115769621355</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04990546078544718</v>
+        <v>0.08097494353803845</v>
       </c>
       <c r="AC11">
-        <v>0.0912522354281028</v>
+        <v>-0.08097494353803845</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AG11">
-        <v>-0.5570000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.03398926654740608</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.2072727272727272</v>
       </c>
       <c r="AJ11">
-        <v>-0.0880910959987348</v>
+        <v>-0.009345794392523366</v>
       </c>
       <c r="AK11">
-        <v>-0.08712654465821994</v>
+        <v>-0.07389162561576355</v>
       </c>
       <c r="AL11">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>396.6666666666666</v>
-      </c>
-      <c r="AP11">
-        <v>-0.4801724137931035</v>
+        <v>-0.073</v>
+      </c>
+      <c r="AQ11">
+        <v>-0</v>
       </c>
     </row>
     <row r="12">
@@ -1883,7 +1889,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Starhedge S.A. (WSE:SHG)</t>
+          <t>Invista S.A. (WSE:NTC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1891,23 +1897,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.302</v>
+      </c>
+      <c r="E12">
+        <v>-0.442</v>
+      </c>
       <c r="G12">
-        <v>0.1224268689057421</v>
+        <v>-0.03798449612403101</v>
       </c>
       <c r="H12">
-        <v>0.1224268689057421</v>
+        <v>-0.03798449612403101</v>
       </c>
       <c r="I12">
-        <v>0.1081256771397616</v>
+        <v>0.01472868217054264</v>
       </c>
       <c r="J12">
-        <v>0.09475460648276376</v>
+        <v>0.01472868217054264</v>
       </c>
       <c r="K12">
-        <v>0.708</v>
+        <v>0.028</v>
       </c>
       <c r="L12">
-        <v>0.07670639219934994</v>
+        <v>0.02170542635658915</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1931,73 +1943,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.209</v>
+        <v>0.015</v>
       </c>
       <c r="V12">
-        <v>0.02163561076604555</v>
+        <v>0.005725190839694656</v>
       </c>
       <c r="W12">
-        <v>0.06742857142857142</v>
+        <v>0.007235142118863049</v>
       </c>
       <c r="X12">
-        <v>0.05784370004036407</v>
+        <v>0.08330836812090016</v>
       </c>
       <c r="Y12">
-        <v>0.00958487138820735</v>
+        <v>-0.07607322600203711</v>
       </c>
       <c r="Z12">
-        <v>0.7196319975050678</v>
+        <v>0.316719862509207</v>
       </c>
       <c r="AA12">
-        <v>0.06818844673599794</v>
+        <v>0.004664866191996072</v>
       </c>
       <c r="AB12">
-        <v>0.05139560780579633</v>
+        <v>0.08680403618890309</v>
       </c>
       <c r="AC12">
-        <v>0.01679283893020161</v>
+        <v>-0.08213916999690701</v>
       </c>
       <c r="AD12">
-        <v>2.72</v>
+        <v>0.196</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.72</v>
+        <v>0.196</v>
       </c>
       <c r="AG12">
-        <v>2.511</v>
+        <v>0.181</v>
       </c>
       <c r="AH12">
-        <v>0.2197092084006462</v>
+        <v>0.06960227272727272</v>
       </c>
       <c r="AI12">
-        <v>0.1666666666666667</v>
+        <v>0.05892964521948287</v>
       </c>
       <c r="AJ12">
-        <v>0.2063100813408923</v>
+        <v>0.06461977865048196</v>
       </c>
       <c r="AK12">
-        <v>0.155856247284464</v>
+        <v>0.05466626396858955</v>
       </c>
       <c r="AL12">
-        <v>0.155</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>2.211382113821138</v>
-      </c>
-      <c r="AO12">
-        <v>6.438709677419355</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="AP12">
-        <v>2.041463414634146</v>
-      </c>
-      <c r="AQ12">
-        <v>8.603448275862069</v>
+        <v>7.541666666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2008,7 +2014,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Magna Polonia S.A. (WSE:06N)</t>
+          <t>BBI Development S.A. (WSE:BBD)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2016,32 +2022,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D13">
+        <v>-0.212</v>
+      </c>
       <c r="G13">
-        <v>0.4495</v>
+        <v>-0.139067055393586</v>
       </c>
       <c r="H13">
-        <v>0.385</v>
+        <v>-0.139067055393586</v>
       </c>
       <c r="I13">
-        <v>0.2045</v>
+        <v>-0.04198250728862973</v>
       </c>
       <c r="J13">
-        <v>0.1355886554621848</v>
+        <v>-0.04198250728862973</v>
       </c>
       <c r="K13">
-        <v>0.474</v>
+        <v>-1.18</v>
       </c>
       <c r="L13">
-        <v>0.237</v>
+        <v>-0.3440233236151603</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>0.018</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.002031602708803612</v>
       </c>
       <c r="O13">
-        <v>-0</v>
+        <v>-0.01525423728813559</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -2050,79 +2059,82 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>0.018</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>0.252</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
-        <v>0.02763157894736842</v>
+        <v>0.255079006772009</v>
       </c>
       <c r="W13">
-        <v>0.0771986970684039</v>
+        <v>-0.03699059561128527</v>
       </c>
       <c r="X13">
-        <v>0.05219609517338942</v>
+        <v>0.1340937884366396</v>
       </c>
       <c r="Y13">
-        <v>0.02500260189501449</v>
+        <v>-0.1710843840479249</v>
       </c>
       <c r="Z13">
-        <v>0.3362474781439139</v>
+        <v>0.08000933053417308</v>
       </c>
       <c r="AA13">
-        <v>0.04559134346408367</v>
+        <v>-0.003358992302309307</v>
       </c>
       <c r="AB13">
-        <v>0.05244174566664924</v>
+        <v>0.08452957371084002</v>
       </c>
       <c r="AC13">
-        <v>-0.006850402202565567</v>
+        <v>-0.08788856601314933</v>
       </c>
       <c r="AD13">
-        <v>0.741</v>
+        <v>13.9</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.741</v>
+        <v>13.9</v>
       </c>
       <c r="AG13">
-        <v>0.489</v>
+        <v>11.64</v>
       </c>
       <c r="AH13">
-        <v>0.07514450867052024</v>
+        <v>0.6107205623901583</v>
       </c>
       <c r="AI13">
-        <v>0.08706379978850899</v>
+        <v>0.3629242819843342</v>
       </c>
       <c r="AJ13">
-        <v>0.05088979082110522</v>
+        <v>0.5678048780487805</v>
       </c>
       <c r="AK13">
-        <v>0.05920813657827824</v>
+        <v>0.3229744728079911</v>
       </c>
       <c r="AL13">
-        <v>0.091</v>
+        <v>1.74</v>
       </c>
       <c r="AM13">
-        <v>-0.3130000000000001</v>
+        <v>1.075</v>
       </c>
       <c r="AN13">
-        <v>1.73943661971831</v>
+        <v>-127.5229357798165</v>
       </c>
       <c r="AO13">
-        <v>4.494505494505495</v>
+        <v>-0.08275862068965517</v>
       </c>
       <c r="AP13">
-        <v>1.147887323943662</v>
+        <v>-106.7889908256881</v>
       </c>
       <c r="AQ13">
-        <v>-1.306709265175719</v>
+        <v>-0.133953488372093</v>
       </c>
     </row>
     <row r="14">
@@ -2133,7 +2145,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caspar Asset Management S.A. (WSE:CSR)</t>
+          <t>Black Pearl S.A. (WSE:BPC)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2142,46 +2154,43 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.4379999999999999</v>
-      </c>
-      <c r="E14">
-        <v>0.9490000000000001</v>
+        <v>-0.355</v>
       </c>
       <c r="G14">
-        <v>6.493506493506494e-05</v>
+        <v>-24.90909090909091</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>-24.90909090909091</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>-10.36363636363637</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>-10.36363636363637</v>
       </c>
       <c r="K14">
-        <v>6.72</v>
+        <v>-0.221</v>
       </c>
       <c r="L14">
-        <v>0.4363636363636363</v>
+        <v>-20.09090909090909</v>
       </c>
       <c r="M14">
-        <v>4.89</v>
+        <v>8.094900000000001</v>
       </c>
       <c r="N14">
-        <v>0.09055555555555556</v>
+        <v>0.6040970149253732</v>
       </c>
       <c r="O14">
-        <v>0.7276785714285714</v>
+        <v>-36.62850678733032</v>
       </c>
       <c r="P14">
-        <v>4.89</v>
+        <v>8.094900000000001</v>
       </c>
       <c r="Q14">
-        <v>0.09055555555555556</v>
+        <v>0.6040970149253732</v>
       </c>
       <c r="R14">
-        <v>0.7276785714285714</v>
+        <v>-36.62850678733032</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2190,64 +2199,67 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2.19</v>
+        <v>0.011</v>
       </c>
       <c r="V14">
-        <v>0.04055555555555555</v>
+        <v>0.0008208955223880597</v>
       </c>
       <c r="W14">
-        <v>1.548387096774194</v>
+        <v>-0.03587662337662337</v>
       </c>
       <c r="X14">
-        <v>0.0500474670654518</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y14">
-        <v>1.498339629708742</v>
+        <v>-0.1166420772037831</v>
       </c>
       <c r="Z14">
-        <v>5.541561712846348</v>
+        <v>0.001841312353531972</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>-0.0190826916638768</v>
       </c>
       <c r="AB14">
-        <v>0.04993945256778783</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AC14">
-        <v>-0.04993945256778783</v>
+        <v>-0.09984814549103654</v>
       </c>
       <c r="AD14">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.272</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>-1.918</v>
+        <v>-0.011</v>
       </c>
       <c r="AH14">
-        <v>0.005011792452830189</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.04235440672687636</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.03682654275949464</v>
+        <v>-0.0008215699454776307</v>
       </c>
       <c r="AK14">
-        <v>-0.4532136105860113</v>
+        <v>-0.002245356195141865</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="AQ14">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>-0</v>
+      </c>
+      <c r="AP14">
+        <v>0.09909909909909909</v>
       </c>
     </row>
     <row r="15">
@@ -2258,7 +2270,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BBI Development S.A. (WSE:BBD)</t>
+          <t>Magna Polonia S.A. (WSE:06N)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2267,25 +2279,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.147</v>
+        <v>0.556</v>
       </c>
       <c r="G15">
-        <v>0.08439531859557867</v>
+        <v>-0.06893939393939394</v>
       </c>
       <c r="H15">
-        <v>0.08439531859557867</v>
+        <v>-0.1787878787878788</v>
       </c>
       <c r="I15">
-        <v>-0.1035110533159948</v>
+        <v>-0.181060606060606</v>
       </c>
       <c r="J15">
-        <v>-0.1035110533159948</v>
+        <v>-0.181060606060606</v>
       </c>
       <c r="K15">
-        <v>-2.85</v>
+        <v>-0.189</v>
       </c>
       <c r="L15">
-        <v>-0.3706111833550065</v>
+        <v>-0.1431818181818182</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2309,73 +2321,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1.19</v>
+        <v>0.105</v>
       </c>
       <c r="V15">
-        <v>0.09370078740157481</v>
+        <v>0.008677685950413223</v>
       </c>
       <c r="W15">
-        <v>-0.07983193277310924</v>
+        <v>-0.02684659090909091</v>
       </c>
       <c r="X15">
-        <v>0.09030720117120013</v>
+        <v>0.08267293977347376</v>
       </c>
       <c r="Y15">
-        <v>-0.1701391339443094</v>
+        <v>-0.1095195306825647</v>
       </c>
       <c r="Z15">
-        <v>0.1551873751336952</v>
+        <v>0.1776103336921421</v>
       </c>
       <c r="AA15">
-        <v>-0.01606360866143321</v>
+        <v>-0.03215823466092572</v>
       </c>
       <c r="AB15">
-        <v>0.05169714395109944</v>
+        <v>0.08109294063384849</v>
       </c>
       <c r="AC15">
-        <v>-0.06776075261253266</v>
+        <v>-0.1132511752947742</v>
       </c>
       <c r="AD15">
-        <v>18.2</v>
+        <v>0.679</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>18.2</v>
+        <v>0.679</v>
       </c>
       <c r="AG15">
-        <v>17.01</v>
+        <v>0.5740000000000001</v>
       </c>
       <c r="AH15">
-        <v>0.5889967637540453</v>
+        <v>0.05313404804757806</v>
       </c>
       <c r="AI15">
-        <v>0.3632734530938124</v>
+        <v>0.1007567888410743</v>
       </c>
       <c r="AJ15">
-        <v>0.5725345001682934</v>
+        <v>0.04528956919678082</v>
       </c>
       <c r="AK15">
-        <v>0.3477816397464731</v>
+        <v>0.08652396744045826</v>
       </c>
       <c r="AL15">
-        <v>1.48</v>
+        <v>0.061</v>
       </c>
       <c r="AM15">
-        <v>1.235</v>
+        <v>-0.284</v>
       </c>
       <c r="AN15">
-        <v>-22.60869565217391</v>
+        <v>-3.03125</v>
       </c>
       <c r="AO15">
-        <v>-0.5378378378378379</v>
+        <v>-3.918032786885246</v>
       </c>
       <c r="AP15">
-        <v>-21.13043478260869</v>
+        <v>-2.5625</v>
       </c>
       <c r="AQ15">
-        <v>-0.6445344129554657</v>
+        <v>0.8415492957746479</v>
       </c>
     </row>
     <row r="16">
@@ -2386,7 +2398,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blumerang Investors S.A. (WSE:BLU)</t>
+          <t>Devo Energy S.A. (WSE:DEV)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2395,25 +2407,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.675</v>
+        <v>0.08</v>
       </c>
       <c r="G16">
-        <v>-19.5</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="H16">
-        <v>-19.5</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="I16">
-        <v>-23.5</v>
+        <v>-0.8588235294117645</v>
       </c>
       <c r="J16">
-        <v>-23.5</v>
+        <v>-0.8588235294117645</v>
       </c>
       <c r="K16">
-        <v>-2.29</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="L16">
-        <v>-1145</v>
+        <v>-1.011764705882353</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2437,73 +2449,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>0.0001785714285714286</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>-1.908333333333333</v>
+        <v>-0.06515151515151514</v>
       </c>
       <c r="X16">
-        <v>0.05195276771093402</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y16">
-        <v>-1.960286101044267</v>
+        <v>-0.1459169689786749</v>
       </c>
       <c r="Z16">
-        <v>0.0007342143906020558</v>
+        <v>0.04796839729119639</v>
       </c>
       <c r="AA16">
-        <v>-0.01725403817914831</v>
+        <v>-0.04119638826185101</v>
       </c>
       <c r="AB16">
-        <v>0.05053172330065155</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AC16">
-        <v>-0.06778576147979985</v>
+        <v>-0.1219618420890108</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.217</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>0.06770255271920089</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1.095152603231598</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0.06754731642337793</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.095409540954096</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>0.1</v>
+        <v>0.021</v>
       </c>
       <c r="AM16">
-        <v>0.08700000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="AN16">
-        <v>-31.28205128205128</v>
+        <v>-0</v>
       </c>
       <c r="AO16">
-        <v>-0.47</v>
+        <v>-3.476190476190476</v>
       </c>
       <c r="AP16">
-        <v>-31.20512820512821</v>
+        <v>-0</v>
       </c>
       <c r="AQ16">
-        <v>-0.5402298850574713</v>
+        <v>-4.5625</v>
       </c>
     </row>
     <row r="17">
@@ -2514,7 +2526,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.W. Trade SA (WSE:MWT)</t>
+          <t>Carpathia Capital S.A. (WSE:CRC)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2522,119 +2534,95 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D17">
-        <v>-0.472</v>
-      </c>
-      <c r="E17">
-        <v>-0.6929999999999999</v>
-      </c>
-      <c r="G17">
-        <v>-0.8688524590163933</v>
-      </c>
-      <c r="H17">
-        <v>-0.8688524590163933</v>
-      </c>
-      <c r="I17">
-        <v>-0.488822652757079</v>
-      </c>
-      <c r="J17">
-        <v>-0.488822652757079</v>
-      </c>
       <c r="K17">
-        <v>0.011</v>
-      </c>
-      <c r="L17">
-        <v>0.01639344262295082</v>
+        <v>-1.47</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.00380952380952381</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>-0.0054421768707483</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>0.008</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.00380952380952381</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>-0.0054421768707483</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>12.8</v>
+        <v>0.215</v>
       </c>
       <c r="V17">
-        <v>1.242718446601942</v>
+        <v>0.1023809523809524</v>
       </c>
       <c r="W17">
-        <v>0.0006918238993710691</v>
+        <v>-0.3006134969325154</v>
       </c>
       <c r="X17">
-        <v>0.05019012214627883</v>
+        <v>0.08138054747896928</v>
       </c>
       <c r="Y17">
-        <v>-0.04949829824690776</v>
+        <v>-0.3819940444114847</v>
       </c>
       <c r="Z17">
-        <v>0.05122919529699191</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>-0.02504199114368606</v>
+        <v>-0.04841628959276018</v>
       </c>
       <c r="AB17">
-        <v>0.04999792727488805</v>
+        <v>0.08087499989673994</v>
       </c>
       <c r="AC17">
-        <v>-0.0750399184185741</v>
+        <v>-0.1292912894895001</v>
       </c>
       <c r="AD17">
-        <v>0.104</v>
+        <v>0.038</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.104</v>
+        <v>0.038</v>
       </c>
       <c r="AG17">
-        <v>-12.696</v>
+        <v>-0.177</v>
       </c>
       <c r="AH17">
-        <v>0.009996155324875048</v>
+        <v>0.01777362020579981</v>
       </c>
       <c r="AI17">
-        <v>0.006664957703153038</v>
+        <v>0.01533494753833737</v>
       </c>
       <c r="AJ17">
-        <v>5.298831385642737</v>
+        <v>-0.09204368174726989</v>
       </c>
       <c r="AK17">
-        <v>-4.52781740370899</v>
+        <v>-0.07821475916924436</v>
       </c>
       <c r="AL17">
-        <v>0.04</v>
+        <v>0.002</v>
       </c>
       <c r="AM17">
-        <v>0.038</v>
-      </c>
-      <c r="AN17">
-        <v>-0.3455149501661129</v>
+        <v>-0.05</v>
       </c>
       <c r="AO17">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="AP17">
-        <v>42.17940199335549</v>
+        <v>-107</v>
       </c>
       <c r="AQ17">
-        <v>-8.631578947368421</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="18">
@@ -2645,7 +2633,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ABS Investment SA (WSE:AIN)</t>
+          <t>Centurion Finance Spólka Akcyjna (WSE:CTF)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2653,26 +2641,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D18">
-        <v>-0.0322</v>
-      </c>
-      <c r="G18">
-        <v>-0.5</v>
-      </c>
-      <c r="H18">
-        <v>-0.5</v>
-      </c>
-      <c r="I18">
-        <v>-0.7383720930232559</v>
-      </c>
-      <c r="J18">
-        <v>-0.7383720930232559</v>
-      </c>
       <c r="K18">
-        <v>-2.45</v>
-      </c>
-      <c r="L18">
-        <v>-14.24418604651163</v>
+        <v>-0.173</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2696,67 +2666,73 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.229</v>
+        <v>0.006</v>
       </c>
       <c r="V18">
-        <v>0.09828326180257511</v>
+        <v>0.0003015075376884422</v>
       </c>
       <c r="W18">
-        <v>-1.123853211009174</v>
+        <v>-0.08480392156862744</v>
       </c>
       <c r="X18">
-        <v>0.05203501721874046</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y18">
-        <v>-1.175888228227915</v>
+        <v>-0.1655693753957872</v>
       </c>
       <c r="Z18">
-        <v>0.05358255451713395</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>-0.03956386292834891</v>
+        <v>-0.06053149606299212</v>
       </c>
       <c r="AB18">
-        <v>0.05038179574913702</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AC18">
-        <v>-0.08994565867748593</v>
+        <v>-0.1412969498901519</v>
       </c>
       <c r="AD18">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>-0.05300000000000002</v>
+        <v>-0.006</v>
       </c>
       <c r="AH18">
-        <v>0.0702314445331205</v>
+        <v>0</v>
       </c>
       <c r="AI18">
-        <v>0.03923316986179224</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>-0.02327624066754502</v>
+        <v>-0.0003015984719010757</v>
       </c>
       <c r="AK18">
-        <v>-0.01245008221752408</v>
+        <v>-0.00352112676056338</v>
       </c>
       <c r="AL18">
-        <v>0.051</v>
+        <v>0.008</v>
       </c>
       <c r="AM18">
-        <v>0.006999999999999999</v>
+        <v>-0.004999999999999999</v>
+      </c>
+      <c r="AN18">
+        <v>-0</v>
       </c>
       <c r="AO18">
-        <v>-2.490196078431373</v>
+        <v>-15.375</v>
+      </c>
+      <c r="AP18">
+        <v>0.04918032786885246</v>
       </c>
       <c r="AQ18">
-        <v>-18.14285714285715</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="19">
@@ -2767,7 +2743,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Centurion Finance Spólka Akcyjna (WSE:CTF)</t>
+          <t>FinTech Ventures S.A. (WSE:FIV)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2775,8 +2751,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G19">
+        <v>-14.95726495726496</v>
+      </c>
+      <c r="H19">
+        <v>-14.95726495726496</v>
+      </c>
+      <c r="I19">
+        <v>-10.68376068376068</v>
+      </c>
+      <c r="J19">
+        <v>-10.66038995726496</v>
+      </c>
       <c r="K19">
-        <v>0.227</v>
+        <v>3.29</v>
+      </c>
+      <c r="L19">
+        <v>28.11965811965812</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2800,73 +2791,73 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.242</v>
+        <v>0.008</v>
       </c>
       <c r="V19">
-        <v>0.01186274509803922</v>
+        <v>0.001413427561837456</v>
       </c>
       <c r="W19">
-        <v>0.1233695652173913</v>
+        <v>0.2860869565217392</v>
       </c>
       <c r="X19">
-        <v>0.05038224441370664</v>
+        <v>0.08941359964765429</v>
       </c>
       <c r="Y19">
-        <v>0.07298732080368465</v>
+        <v>0.1966733568740849</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>0.01051969070311095</v>
       </c>
       <c r="AA19">
-        <v>-0.05835726593911545</v>
+        <v>-0.1121440051249775</v>
       </c>
       <c r="AB19">
-        <v>0.05089251241328602</v>
+        <v>0.08263976752374189</v>
       </c>
       <c r="AC19">
-        <v>-0.1092497783524015</v>
+        <v>-0.1947837726487194</v>
       </c>
       <c r="AD19">
-        <v>0.345</v>
+        <v>1.44</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0.345</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>0.103</v>
+        <v>1.432</v>
       </c>
       <c r="AH19">
-        <v>0.01663051337671728</v>
+        <v>0.2028169014084507</v>
       </c>
       <c r="AI19">
-        <v>0.1452631578947368</v>
+        <v>0.1018387553041018</v>
       </c>
       <c r="AJ19">
-        <v>0.005023655074867092</v>
+        <v>0.2019176536943034</v>
       </c>
       <c r="AK19">
-        <v>0.04828879512423815</v>
+        <v>0.1013303141805831</v>
       </c>
       <c r="AL19">
-        <v>0.004</v>
+        <v>0.301</v>
       </c>
       <c r="AM19">
-        <v>-0.008</v>
+        <v>0.278</v>
       </c>
       <c r="AN19">
-        <v>-2.738095238095238</v>
+        <v>-2.054208273894436</v>
       </c>
       <c r="AO19">
-        <v>-31.75</v>
+        <v>-4.152823920265781</v>
       </c>
       <c r="AP19">
-        <v>-0.8174603174603173</v>
+        <v>-2.042796005706134</v>
       </c>
       <c r="AQ19">
-        <v>15.875</v>
+        <v>-4.496402877697842</v>
       </c>
     </row>
     <row r="20">
@@ -2877,7 +2868,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Carpathia Capital S.A. (WSE:CRC)</t>
+          <t>Soho Development S.A. (WSE:SHD)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2885,95 +2876,119 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D20">
+        <v>-0.552</v>
+      </c>
       <c r="E20">
-        <v>0.484</v>
+        <v>0.0803</v>
+      </c>
+      <c r="G20">
+        <v>-3.165680473372781</v>
+      </c>
+      <c r="H20">
+        <v>-3.165680473372781</v>
+      </c>
+      <c r="I20">
+        <v>-2.331360946745562</v>
+      </c>
+      <c r="J20">
+        <v>-2.31803888419273</v>
       </c>
       <c r="K20">
-        <v>1.03</v>
+        <v>2.44</v>
+      </c>
+      <c r="L20">
+        <v>7.218934911242603</v>
       </c>
       <c r="M20">
-        <v>0.165</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.04004854368932039</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.1601941747572816</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>0.165</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.04004854368932039</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.1601941747572816</v>
+        <v>-0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
       <c r="U20">
-        <v>0.47</v>
+        <v>3.15</v>
       </c>
       <c r="V20">
-        <v>0.1140776699029126</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="W20">
-        <v>0.251219512195122</v>
+        <v>0.3771251931993818</v>
       </c>
       <c r="X20">
-        <v>0.04990546078544718</v>
+        <v>0.0810755564438615</v>
       </c>
       <c r="Y20">
-        <v>0.2013140514096748</v>
+        <v>0.2960496367555203</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>0.05841686830279987</v>
       </c>
       <c r="AA20">
-        <v>-0.07500607387140902</v>
+        <v>-0.1354125722186559</v>
       </c>
       <c r="AB20">
-        <v>0.04990546078544718</v>
+        <v>0.0808489992385116</v>
       </c>
       <c r="AC20">
-        <v>-0.1249115346568562</v>
+        <v>-0.2162615714571675</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AG20">
-        <v>-0.47</v>
+        <v>-3.124</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.009040333796940195</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>0.007250418293363078</v>
       </c>
       <c r="AJ20">
-        <v>-0.1287671232876712</v>
+        <v>11.4014598540146</v>
       </c>
       <c r="AK20">
-        <v>-0.1063348416289593</v>
+        <v>-7.1651376146789</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AM20">
-        <v>-0.045</v>
+        <v>-0.003999999999999998</v>
+      </c>
+      <c r="AN20">
+        <v>-0.03341902313624678</v>
+      </c>
+      <c r="AO20">
+        <v>-56.28571428571428</v>
+      </c>
+      <c r="AP20">
+        <v>4.015424164524422</v>
       </c>
       <c r="AQ20">
-        <v>7.422222222222222</v>
+        <v>197.0000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -2984,7 +2999,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Open Finance S.A. (WSE:OPF)</t>
+          <t>Skarbiec Holding S.A. (WSE:SKH)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2993,25 +3008,25 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.138</v>
+        <v>-0.0713</v>
       </c>
       <c r="G21">
-        <v>0.003412073490813648</v>
+        <v>0.2462585034013606</v>
       </c>
       <c r="H21">
-        <v>0.003412073490813648</v>
+        <v>0.2462585034013606</v>
       </c>
       <c r="I21">
-        <v>-0.1724409448818898</v>
+        <v>-0.04312925170068028</v>
       </c>
       <c r="J21">
-        <v>-0.1724409448818898</v>
+        <v>-0.04312925170068028</v>
       </c>
       <c r="K21">
-        <v>-12.8</v>
+        <v>-1.38</v>
       </c>
       <c r="L21">
-        <v>-0.3359580052493438</v>
+        <v>-0.09387755102040816</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -3035,73 +3050,73 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0.454</v>
+        <v>20.4</v>
       </c>
       <c r="V21">
-        <v>0.375206611570248</v>
+        <v>0.6891891891891891</v>
       </c>
       <c r="W21">
-        <v>-0.810126582278481</v>
+        <v>-0.026953125</v>
       </c>
       <c r="X21">
-        <v>1.0750844875568</v>
+        <v>0.08148663582218676</v>
       </c>
       <c r="Y21">
-        <v>-1.885211069835282</v>
+        <v>-0.1084397608221868</v>
       </c>
       <c r="Z21">
-        <v>0.8297941849068933</v>
+        <v>3.213817227809359</v>
       </c>
       <c r="AA21">
-        <v>-0.1430904933028422</v>
+        <v>-0.1386095321381723</v>
       </c>
       <c r="AB21">
-        <v>0.05890809372707912</v>
+        <v>0.08089350133623706</v>
       </c>
       <c r="AC21">
-        <v>-0.2019985870299213</v>
+        <v>-0.2195030334744094</v>
       </c>
       <c r="AD21">
-        <v>44</v>
+        <v>0.628</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>44</v>
+        <v>0.628</v>
       </c>
       <c r="AG21">
-        <v>43.546</v>
+        <v>-19.772</v>
       </c>
       <c r="AH21">
-        <v>0.9732360097323601</v>
+        <v>0.02077543998941379</v>
       </c>
       <c r="AI21">
-        <v>0.9468474284484614</v>
+        <v>0.01557230708192819</v>
       </c>
       <c r="AJ21">
-        <v>0.9729645187237466</v>
+        <v>-2.011803011803011</v>
       </c>
       <c r="AK21">
-        <v>0.9463230180806677</v>
+        <v>-0.9921718185467681</v>
       </c>
       <c r="AL21">
-        <v>1.54</v>
+        <v>0.021</v>
       </c>
       <c r="AM21">
-        <v>1.525</v>
+        <v>-0.362</v>
       </c>
       <c r="AN21">
-        <v>-8.239700374531836</v>
+        <v>-1.37719298245614</v>
       </c>
       <c r="AO21">
-        <v>-4.266233766233766</v>
+        <v>-30.19047619047619</v>
       </c>
       <c r="AP21">
-        <v>-8.154681647940075</v>
+        <v>43.35964912280701</v>
       </c>
       <c r="AQ21">
-        <v>-4.308196721311475</v>
+        <v>1.751381215469613</v>
       </c>
     </row>
     <row r="22">
@@ -3112,7 +3127,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Soho Development S.A. (WSE:SHD)</t>
+          <t>Open Finance S.A. (WSE:OPF)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3121,25 +3136,25 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.4429999999999999</v>
+        <v>-0.342</v>
       </c>
       <c r="G22">
-        <v>-3.40153452685422</v>
+        <v>-0.3392181588902901</v>
       </c>
       <c r="H22">
-        <v>-3.40153452685422</v>
+        <v>-0.3392181588902901</v>
       </c>
       <c r="I22">
-        <v>-3.554987212276215</v>
+        <v>-0.6191677175283733</v>
       </c>
       <c r="J22">
-        <v>-3.554987212276215</v>
+        <v>-0.6191677175283733</v>
       </c>
       <c r="K22">
-        <v>-1.36</v>
+        <v>-28.4</v>
       </c>
       <c r="L22">
-        <v>-3.478260869565217</v>
+        <v>-3.581336696090794</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3163,73 +3178,73 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0.785</v>
+        <v>0.372</v>
       </c>
       <c r="V22">
-        <v>0.2813620071684588</v>
+        <v>1.9375</v>
       </c>
       <c r="W22">
-        <v>-0.1801324503311258</v>
+        <v>-11.49797570850202</v>
       </c>
       <c r="X22">
-        <v>0.05092604671622045</v>
+        <v>6.29493117132705</v>
       </c>
       <c r="Y22">
-        <v>-0.2310584970473463</v>
+        <v>-17.79290687982908</v>
       </c>
       <c r="Z22">
-        <v>0.06103652825476116</v>
+        <v>0.2220293425915556</v>
       </c>
       <c r="AA22">
-        <v>-0.2169840774274118</v>
+        <v>-0.1374734012767387</v>
       </c>
       <c r="AB22">
-        <v>0.05014240938242464</v>
+        <v>0.0990597900539176</v>
       </c>
       <c r="AC22">
-        <v>-0.2671264868098364</v>
+        <v>-0.2365331913306563</v>
       </c>
       <c r="AD22">
-        <v>0.101</v>
+        <v>35.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0.101</v>
+        <v>35.1</v>
       </c>
       <c r="AG22">
-        <v>-0.6840000000000001</v>
+        <v>34.728</v>
       </c>
       <c r="AH22">
-        <v>0.03493600830162574</v>
+        <v>0.9945596735804149</v>
       </c>
       <c r="AI22">
-        <v>0.01537056764571603</v>
+        <v>4.178571428571428</v>
       </c>
       <c r="AJ22">
-        <v>-0.3247863247863249</v>
+        <v>0.9945017182130584</v>
       </c>
       <c r="AK22">
-        <v>-0.1182163843760802</v>
+        <v>4.325859491778774</v>
       </c>
       <c r="AL22">
-        <v>0.028</v>
+        <v>0.667</v>
       </c>
       <c r="AM22">
-        <v>0.021</v>
+        <v>0.666</v>
       </c>
       <c r="AN22">
-        <v>-0.07318840579710147</v>
+        <v>-8.032036613272311</v>
       </c>
       <c r="AO22">
-        <v>-49.64285714285714</v>
+        <v>-7.361319340329834</v>
       </c>
       <c r="AP22">
-        <v>0.4956521739130436</v>
+        <v>-7.946910755148742</v>
       </c>
       <c r="AQ22">
-        <v>-66.19047619047618</v>
+        <v>-7.372372372372372</v>
       </c>
     </row>
     <row r="23">
@@ -3240,7 +3255,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SPARK VC S.A. (WSE:SPK)</t>
+          <t>M.W. Trade SA (WSE:MWT)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3248,17 +3263,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D23">
+        <v>-0.524</v>
+      </c>
+      <c r="G23">
+        <v>-0.5964912280701754</v>
+      </c>
+      <c r="H23">
+        <v>-0.5964912280701754</v>
+      </c>
+      <c r="I23">
+        <v>-1.934210526315789</v>
+      </c>
+      <c r="J23">
+        <v>-1.934210526315789</v>
+      </c>
       <c r="K23">
-        <v>-0.032</v>
+        <v>-0.527</v>
+      </c>
+      <c r="L23">
+        <v>-2.31140350877193</v>
       </c>
       <c r="M23">
-        <v>-0</v>
+        <v>5.94</v>
       </c>
       <c r="N23">
-        <v>-0</v>
+        <v>2.302325581395349</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>-11.27134724857685</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3270,70 +3303,79 @@
         <v>0</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>5.94</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
       </c>
       <c r="U23">
-        <v>0.003</v>
+        <v>4.53</v>
       </c>
       <c r="V23">
-        <v>7.957559681697613e-05</v>
+        <v>1.755813953488372</v>
       </c>
       <c r="W23">
-        <v>-0.3106796116504855</v>
+        <v>-0.034</v>
       </c>
       <c r="X23">
-        <v>0.04991667792997087</v>
+        <v>0.08267585791708221</v>
       </c>
       <c r="Y23">
-        <v>-0.3605962895804563</v>
+        <v>-0.1166758579170822</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>0.08131241084165483</v>
       </c>
       <c r="AA23">
-        <v>-0.25</v>
+        <v>-0.1572753209700429</v>
       </c>
       <c r="AB23">
-        <v>0.04990913977471439</v>
+        <v>0.08125719846289658</v>
       </c>
       <c r="AC23">
-        <v>-0.2999091397747144</v>
+        <v>-0.2385325194329395</v>
       </c>
       <c r="AD23">
-        <v>0.015</v>
+        <v>0.145</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>0.015</v>
+        <v>0.145</v>
       </c>
       <c r="AG23">
-        <v>0.012</v>
+        <v>-4.385000000000001</v>
       </c>
       <c r="AH23">
-        <v>0.0003977197401564364</v>
+        <v>0.05321100917431192</v>
       </c>
       <c r="AI23">
-        <v>0.1041666666666667</v>
+        <v>0.02375102375102375</v>
       </c>
       <c r="AJ23">
-        <v>0.0003182011030971574</v>
+        <v>2.429362880886426</v>
       </c>
       <c r="AK23">
-        <v>0.0851063829787234</v>
+        <v>-2.784126984126986</v>
       </c>
       <c r="AL23">
-        <v>0.001</v>
+        <v>0.118</v>
       </c>
       <c r="AM23">
-        <v>0.001</v>
+        <v>0.05399999999999999</v>
+      </c>
+      <c r="AN23">
+        <v>-0.3436018957345972</v>
       </c>
       <c r="AO23">
-        <v>-30</v>
+        <v>-3.737288135593221</v>
+      </c>
+      <c r="AP23">
+        <v>10.39099526066351</v>
       </c>
       <c r="AQ23">
-        <v>-30</v>
+        <v>-8.166666666666668</v>
       </c>
     </row>
     <row r="24">
@@ -3344,7 +3386,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Agencja Rozwoju Innowacji Spólka Akcyjna (WSE:ARI)</t>
+          <t>SPARK VC S.A. (WSE:SPK)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3352,35 +3394,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D24">
-        <v>0.0135</v>
-      </c>
-      <c r="G24">
-        <v>0.0796812749003984</v>
-      </c>
-      <c r="H24">
-        <v>0.0796812749003984</v>
-      </c>
-      <c r="I24">
-        <v>0.346613545816733</v>
-      </c>
-      <c r="J24">
-        <v>0.346613545816733</v>
-      </c>
       <c r="K24">
-        <v>0.024</v>
-      </c>
-      <c r="L24">
-        <v>0.09561752988047809</v>
+        <v>-0.027</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>0.048</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.0007339449541284404</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>-1.777777777777778</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3389,79 +3413,76 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>0.048</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.529051987767584e-05</v>
       </c>
       <c r="W24">
-        <v>-0.08510638297872342</v>
+        <v>-0.2093023255813953</v>
       </c>
       <c r="X24">
-        <v>0.05135423809064141</v>
+        <v>0.08077169089460928</v>
       </c>
       <c r="Y24">
-        <v>-0.1364606210693648</v>
+        <v>-0.2900740164760046</v>
       </c>
       <c r="Z24">
-        <v>-1.028688524590164</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>-0.3565573770491803</v>
+        <v>-0.1773049645390071</v>
       </c>
       <c r="AB24">
-        <v>0.05035758442858917</v>
+        <v>0.08076714918724222</v>
       </c>
       <c r="AC24">
-        <v>-0.4069149614777695</v>
+        <v>-0.2580721137262493</v>
       </c>
       <c r="AD24">
-        <v>0.111</v>
+        <v>0.012</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0.111</v>
+        <v>0.012</v>
       </c>
       <c r="AG24">
-        <v>0.111</v>
+        <v>0.011</v>
       </c>
       <c r="AH24">
-        <v>0.04887714663143989</v>
+        <v>0.000183452577508714</v>
       </c>
       <c r="AI24">
-        <v>-1.247191011235955</v>
+        <v>0.09917355371900827</v>
       </c>
       <c r="AJ24">
-        <v>0.04887714663143989</v>
+        <v>0.0001681674336120836</v>
       </c>
       <c r="AK24">
-        <v>-1.247191011235955</v>
+        <v>0.09166666666666666</v>
       </c>
       <c r="AL24">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="AM24">
-        <v>0.006</v>
-      </c>
-      <c r="AN24">
-        <v>1.321428571428571</v>
+        <v>0.001</v>
       </c>
       <c r="AO24">
-        <v>14.5</v>
-      </c>
-      <c r="AP24">
-        <v>1.321428571428571</v>
+        <v>-25</v>
       </c>
       <c r="AQ24">
-        <v>14.5</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="25">
@@ -3472,7 +3493,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ONE S.A. (WSE:FMG)</t>
+          <t>Adiuvo Investments S.A. (WSE:ADV)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3481,25 +3502,25 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.277</v>
+        <v>-0.271</v>
       </c>
       <c r="G25">
-        <v>-0.1549497847919656</v>
+        <v>-10.46728971962617</v>
       </c>
       <c r="H25">
-        <v>-0.1549497847919656</v>
+        <v>-15.98130841121495</v>
       </c>
       <c r="I25">
-        <v>-0.2783357245337159</v>
+        <v>-4.672897196261682</v>
       </c>
       <c r="J25">
-        <v>-0.2783357245337159</v>
+        <v>-4.672897196261682</v>
       </c>
       <c r="K25">
-        <v>-7.29</v>
+        <v>-1.78</v>
       </c>
       <c r="L25">
-        <v>-1.045911047345768</v>
+        <v>-5.545171339563863</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3523,73 +3544,73 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>0.29</v>
+        <v>0.006</v>
       </c>
       <c r="V25">
-        <v>0.3972602739726027</v>
+        <v>0.002678571428571428</v>
       </c>
       <c r="W25">
-        <v>-1.980978260869565</v>
+        <v>-3.490196078431373</v>
       </c>
       <c r="X25">
-        <v>0.1460686578514313</v>
+        <v>0.1945780127557292</v>
       </c>
       <c r="Y25">
-        <v>-2.127046918720997</v>
+        <v>-3.684774091187102</v>
       </c>
       <c r="Z25">
-        <v>1.32258064516129</v>
+        <v>0.03721739130434783</v>
       </c>
       <c r="AA25">
-        <v>-0.3681214421252372</v>
+        <v>-0.1739130434782609</v>
       </c>
       <c r="AB25">
-        <v>0.05705856988959061</v>
+        <v>0.08551140439918509</v>
       </c>
       <c r="AC25">
-        <v>-0.4251800120148278</v>
+        <v>-0.259424447877446</v>
       </c>
       <c r="AD25">
-        <v>2.49</v>
+        <v>7.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>2.49</v>
+        <v>7.5</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>7.494</v>
       </c>
       <c r="AH25">
-        <v>0.7732919254658386</v>
+        <v>0.7700205338809035</v>
       </c>
       <c r="AI25">
-        <v>1.43598615916955</v>
+        <v>1.070052789270937</v>
       </c>
       <c r="AJ25">
-        <v>0.7508532423208192</v>
+        <v>0.7698787754263406</v>
       </c>
       <c r="AK25">
-        <v>1.523545706371191</v>
+        <v>1.07011280879623</v>
       </c>
       <c r="AL25">
-        <v>0.318</v>
+        <v>0.623</v>
       </c>
       <c r="AM25">
-        <v>0.258</v>
+        <v>0.591</v>
       </c>
       <c r="AN25">
-        <v>-1.52760736196319</v>
+        <v>-5.244755244755245</v>
       </c>
       <c r="AO25">
-        <v>-6.10062893081761</v>
+        <v>-2.407704654895666</v>
       </c>
       <c r="AP25">
-        <v>-1.349693251533743</v>
+        <v>-5.240559440559441</v>
       </c>
       <c r="AQ25">
-        <v>-7.519379844961239</v>
+        <v>-2.538071065989848</v>
       </c>
     </row>
     <row r="26">
@@ -3600,7 +3621,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adiuvo Investments S.A. (WSE:ADV)</t>
+          <t>Dr.Finance S.A. (WSE:DRF)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3609,34 +3630,34 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.278</v>
+        <v>0.107</v>
       </c>
       <c r="G26">
-        <v>-3.385826771653544</v>
+        <v>0.02487562189054727</v>
       </c>
       <c r="H26">
-        <v>-8.661417322834646</v>
+        <v>0.02487562189054727</v>
       </c>
       <c r="I26">
-        <v>-19.7244094488189</v>
+        <v>-0.01890547263681592</v>
       </c>
       <c r="J26">
-        <v>-19.7244094488189</v>
+        <v>-0.01890547263681592</v>
       </c>
       <c r="K26">
-        <v>-6.43</v>
+        <v>-0.046</v>
       </c>
       <c r="L26">
-        <v>-25.31496062992126</v>
+        <v>-0.02288557213930349</v>
       </c>
       <c r="M26">
-        <v>-0</v>
+        <v>0.001</v>
       </c>
       <c r="N26">
-        <v>-0</v>
+        <v>0.001757469244288225</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>-0.02173913043478261</v>
       </c>
       <c r="P26">
         <v>-0</v>
@@ -3648,76 +3669,73 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>0.001</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
       </c>
       <c r="U26">
-        <v>0.035</v>
+        <v>0.078</v>
       </c>
       <c r="V26">
-        <v>0.004358655043586551</v>
+        <v>0.1370826010544816</v>
       </c>
       <c r="W26">
-        <v>-0.9483775811209438</v>
+        <v>-0.2100456621004566</v>
       </c>
       <c r="X26">
-        <v>0.07851919047101749</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y26">
-        <v>-1.026896771591961</v>
+        <v>-0.2908111159276163</v>
       </c>
       <c r="Z26">
-        <v>0.02016513178786917</v>
+        <v>32.41935483870967</v>
       </c>
       <c r="AA26">
-        <v>-0.3977453159733249</v>
+        <v>-0.6129032258064516</v>
       </c>
       <c r="AB26">
-        <v>0.05332179185667183</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AC26">
-        <v>-0.4510671078299967</v>
+        <v>-0.6936686796336113</v>
       </c>
       <c r="AD26">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>8.115</v>
+        <v>-0.078</v>
       </c>
       <c r="AH26">
-        <v>0.5037082818294191</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>0.7859209257473481</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>0.5026323939300094</v>
+        <v>-0.1588594704684318</v>
       </c>
       <c r="AK26">
-        <v>0.7851959361393324</v>
+        <v>-1.5</v>
       </c>
       <c r="AL26">
-        <v>0.427</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>-1.639839034205232</v>
-      </c>
-      <c r="AO26">
-        <v>-11.73302107728337</v>
+        <v>-0</v>
       </c>
       <c r="AP26">
-        <v>-1.632796780684105</v>
-      </c>
-      <c r="AQ26">
-        <v>-12.30958230958231</v>
+        <v>2.108108108108108</v>
       </c>
     </row>
     <row r="27">
@@ -3728,7 +3746,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Shockwork Games S.A. (WSE:SWK)</t>
+          <t>Metaversum S.A. (WSE:MET)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3737,25 +3755,25 @@
         </is>
       </c>
       <c r="D27">
-        <v>-0.27</v>
+        <v>0.199</v>
       </c>
       <c r="G27">
-        <v>3.75</v>
+        <v>0.5319148936170213</v>
       </c>
       <c r="H27">
-        <v>3.75</v>
+        <v>0.5319148936170213</v>
       </c>
       <c r="I27">
-        <v>-7.5</v>
+        <v>-0.6808510638297872</v>
       </c>
       <c r="J27">
-        <v>-7.5</v>
+        <v>-0.6808510638297872</v>
       </c>
       <c r="K27">
-        <v>0.031</v>
+        <v>-0.032</v>
       </c>
       <c r="L27">
-        <v>7.75</v>
+        <v>-0.6808510638297872</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3764,7 +3782,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3773,67 +3791,73 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>0.001785714285714286</v>
       </c>
       <c r="W27">
-        <v>0.8611111111111112</v>
+        <v>-5.333333333333333</v>
       </c>
       <c r="X27">
-        <v>0.04990546078544718</v>
+        <v>0.08197945445573115</v>
       </c>
       <c r="Y27">
-        <v>0.8112056503256639</v>
+        <v>-5.415312787789064</v>
       </c>
       <c r="Z27">
-        <v>0.1111111111111111</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="AA27">
-        <v>-0.8333333333333334</v>
+        <v>-5.333333333333333</v>
       </c>
       <c r="AB27">
-        <v>0.04990546078544718</v>
+        <v>0.08097798513093689</v>
       </c>
       <c r="AC27">
-        <v>-0.8832387941187806</v>
+        <v>-5.41431131846427</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>0.03448275862068965</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>0.1834862385321101</v>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>0.03281519861830742</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>0.1759259259259259</v>
       </c>
       <c r="AL27">
         <v>0</v>
       </c>
       <c r="AM27">
         <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>-1.6</v>
+      </c>
+      <c r="AP27">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="28">
@@ -3844,7 +3868,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nexity Global S.A. (WSE:NXG)</t>
+          <t>ABS Investment ASI SA (WSE:AIN)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3852,26 +3876,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D28">
-        <v>0.354</v>
-      </c>
-      <c r="G28">
-        <v>-5.188524590163935</v>
-      </c>
-      <c r="H28">
-        <v>-5.188524590163935</v>
-      </c>
-      <c r="I28">
-        <v>-13.11475409836066</v>
-      </c>
-      <c r="J28">
-        <v>-13.11475409836066</v>
-      </c>
       <c r="K28">
-        <v>-1.38</v>
-      </c>
-      <c r="L28">
-        <v>-11.31147540983607</v>
+        <v>-0.638</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3895,73 +3901,49 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.119</v>
+        <v>0.074</v>
       </c>
       <c r="V28">
-        <v>0.01983333333333333</v>
-      </c>
-      <c r="W28">
-        <v>-0.8961038961038961</v>
+        <v>0.04180790960451977</v>
       </c>
       <c r="X28">
-        <v>0.0559668317812328</v>
-      </c>
-      <c r="Y28">
-        <v>-0.9520707278851289</v>
-      </c>
-      <c r="Z28">
-        <v>0.1121323529411765</v>
-      </c>
-      <c r="AA28">
-        <v>-1.470588235294118</v>
+        <v>0.08376136046309191</v>
       </c>
       <c r="AB28">
-        <v>0.05154232839838403</v>
-      </c>
-      <c r="AC28">
-        <v>-1.522130563692502</v>
+        <v>0.08126467065908485</v>
       </c>
       <c r="AD28">
-        <v>1.29</v>
+        <v>0.156</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.29</v>
+        <v>0.156</v>
       </c>
       <c r="AG28">
-        <v>1.171</v>
+        <v>0.082</v>
       </c>
       <c r="AH28">
-        <v>0.1769547325102881</v>
+        <v>0.0809968847352025</v>
       </c>
       <c r="AI28">
-        <v>0.9174964438122333</v>
+        <v>0.05172413793103448</v>
       </c>
       <c r="AJ28">
-        <v>0.163296611351276</v>
+        <v>0.04427645788336933</v>
       </c>
       <c r="AK28">
-        <v>0.9098679098679098</v>
+        <v>0.02787219578518015</v>
       </c>
       <c r="AL28">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>-0.002999999999999999</v>
-      </c>
-      <c r="AN28">
-        <v>-0.8164556962025317</v>
-      </c>
-      <c r="AO28">
-        <v>-84.21052631578948</v>
-      </c>
-      <c r="AP28">
-        <v>-0.7411392405063291</v>
+        <v>-0.024</v>
       </c>
       <c r="AQ28">
-        <v>533.3333333333335</v>
+        <v>5.458333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -3972,7 +3954,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Baltic Bridge Spólka Akcyjna (WSE:WIS)</t>
+          <t>Grupa Trinity S.A. (WSE:GTY)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3980,8 +3962,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>-17</v>
+      </c>
+      <c r="J29">
+        <v>-17</v>
+      </c>
       <c r="K29">
-        <v>-1.38</v>
+        <v>-0.045</v>
+      </c>
+      <c r="L29">
+        <v>-45</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -4005,31 +4002,22 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.008999999999999999</v>
+        <v>0.001</v>
       </c>
       <c r="V29">
-        <v>0.005172413793103448</v>
+        <v>0.0007936507936507937</v>
       </c>
       <c r="W29">
-        <v>-2.459893048128342</v>
+        <v>0.7894736842105262</v>
       </c>
       <c r="X29">
-        <v>0.04990546078544718</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y29">
-        <v>-2.509798508913789</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>-2.536231884057971</v>
+        <v>0.7087082303833665</v>
       </c>
       <c r="AB29">
-        <v>0.04990546078544718</v>
-      </c>
-      <c r="AC29">
-        <v>-2.586137344843418</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AD29">
         <v>0</v>
@@ -4041,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>-0.008999999999999999</v>
+        <v>-0.001</v>
       </c>
       <c r="AH29">
         <v>0</v>
@@ -4050,28 +4038,22 @@
         <v>-0</v>
       </c>
       <c r="AJ29">
-        <v>-0.005199306759098786</v>
+        <v>-0.0007942811755361397</v>
       </c>
       <c r="AK29">
-        <v>0.01071428571428571</v>
+        <v>0.0108695652173913</v>
       </c>
       <c r="AL29">
-        <v>0.012</v>
+        <v>0.004</v>
       </c>
       <c r="AM29">
-        <v>0.008</v>
-      </c>
-      <c r="AN29">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="AO29">
-        <v>-116.6666666666667</v>
-      </c>
-      <c r="AP29">
-        <v>0.006428571428571428</v>
+        <v>-4.25</v>
       </c>
       <c r="AQ29">
-        <v>-175</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="30">
@@ -4082,7 +4064,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grupa Trinity S.A. (WSE:GTY)</t>
+          <t>Baltic Bridge Spólka Akcyjna (WSE:WIS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4090,29 +4072,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D30">
-        <v>-0.199</v>
-      </c>
-      <c r="E30">
-        <v>-0.138</v>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0.9581056466302368</v>
-      </c>
-      <c r="J30">
-        <v>0.9581056466302368</v>
-      </c>
       <c r="K30">
-        <v>0.493</v>
-      </c>
-      <c r="L30">
-        <v>0.8979963570127504</v>
+        <v>-0.134</v>
       </c>
       <c r="M30">
         <v>-0</v>
@@ -4121,7 +4082,7 @@
         <v>-0</v>
       </c>
       <c r="O30">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P30">
         <v>-0</v>
@@ -4130,73 +4091,70 @@
         <v>-0</v>
       </c>
       <c r="R30">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="U30">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
       <c r="V30">
-        <v>0.0009280742459396753</v>
+        <v>0.01192660550458715</v>
       </c>
       <c r="W30">
-        <v>-0.8710247349823322</v>
+        <v>0.161251504211793</v>
       </c>
       <c r="X30">
-        <v>0.05021289556319705</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="Y30">
-        <v>-0.9212376305455293</v>
-      </c>
-      <c r="Z30">
-        <v>-34.31250000000021</v>
-      </c>
-      <c r="AA30">
-        <v>-32.8750000000002</v>
+        <v>0.0804860503846333</v>
       </c>
       <c r="AB30">
-        <v>0.05000524496064428</v>
-      </c>
-      <c r="AC30">
-        <v>-32.92500524496084</v>
+        <v>0.08076545382715974</v>
       </c>
       <c r="AD30">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>0.043</v>
+        <v>-0.013</v>
       </c>
       <c r="AH30">
-        <v>0.01078723892586642</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>-4.699999999999999</v>
+        <v>-0</v>
       </c>
       <c r="AJ30">
-        <v>0.009878244888582587</v>
+        <v>-0.01207056638811513</v>
       </c>
       <c r="AK30">
-        <v>-3.07142857142857</v>
+        <v>0.01591187270501836</v>
       </c>
       <c r="AL30">
-        <v>0.036</v>
+        <v>0.008</v>
       </c>
       <c r="AM30">
-        <v>0.03299999999999999</v>
+        <v>0.008</v>
+      </c>
+      <c r="AN30">
+        <v>-0</v>
       </c>
       <c r="AO30">
-        <v>14.61111111111111</v>
+        <v>-11.875</v>
+      </c>
+      <c r="AP30">
+        <v>0.1368421052631579</v>
       </c>
       <c r="AQ30">
-        <v>15.93939393939394</v>
+        <v>-11.875</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.029425</v>
+        <v>-0.02445</v>
       </c>
       <c r="E2">
-        <v>-0.10285</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G2">
-        <v>0.8830614346944877</v>
+        <v>0.1386349556519243</v>
       </c>
       <c r="H2">
-        <v>0.867146227198724</v>
+        <v>0.006890195071092915</v>
       </c>
       <c r="I2">
-        <v>0.0502209522543775</v>
+        <v>0.2668137380819268</v>
       </c>
       <c r="J2">
-        <v>0.04797711511143676</v>
+        <v>0.2461785834322747</v>
       </c>
       <c r="K2">
-        <v>-14.057</v>
+        <v>6.732</v>
       </c>
       <c r="L2">
-        <v>-0.1167641293152141</v>
+        <v>0.1017210377600822</v>
       </c>
       <c r="M2">
-        <v>28.6244</v>
+        <v>4.565</v>
       </c>
       <c r="N2">
-        <v>0.05686654309729995</v>
+        <v>0.01880326390061662</v>
       </c>
       <c r="O2">
-        <v>-2.036309312086505</v>
+        <v>0.6781045751633987</v>
       </c>
       <c r="P2">
-        <v>17.6464</v>
+        <v>1.668</v>
       </c>
       <c r="Q2">
-        <v>0.03505714586549216</v>
+        <v>0.006870502559962434</v>
       </c>
       <c r="R2">
-        <v>-1.255346090915558</v>
+        <v>0.2477718360071301</v>
       </c>
       <c r="S2">
-        <v>10.978</v>
+        <v>2.897</v>
       </c>
       <c r="T2">
-        <v>0.3835189558558432</v>
+        <v>0.6346111719605696</v>
       </c>
       <c r="U2">
-        <v>60.635</v>
+        <v>59.484</v>
       </c>
       <c r="V2">
-        <v>0.120460266091334</v>
+        <v>0.2450149725880129</v>
       </c>
       <c r="W2">
-        <v>-0.02689985795454546</v>
+        <v>-0.005116658088866014</v>
       </c>
       <c r="X2">
-        <v>0.08144168498810182</v>
+        <v>0.06902409339657056</v>
       </c>
       <c r="Y2">
-        <v>-0.1083415429426473</v>
+        <v>-0.07414075148543657</v>
       </c>
       <c r="Z2">
-        <v>0.1665345600573246</v>
+        <v>0.6822431833410649</v>
       </c>
       <c r="AA2">
-        <v>-0.04480633892730559</v>
+        <v>-0.1043148903892434</v>
       </c>
       <c r="AB2">
-        <v>0.08088425061648849</v>
+        <v>0.06870046363045976</v>
       </c>
       <c r="AC2">
-        <v>-0.1256265657892554</v>
+        <v>-0.1787803769936189</v>
       </c>
       <c r="AD2">
-        <v>113.389</v>
+        <v>29.952</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>113.389</v>
+        <v>29.952</v>
       </c>
       <c r="AG2">
-        <v>52.754</v>
+        <v>-29.532</v>
       </c>
       <c r="AH2">
-        <v>0.1838492095662748</v>
+        <v>0.1098233044524051</v>
       </c>
       <c r="AI2">
-        <v>0.1765636508309729</v>
+        <v>0.1644810543657331</v>
       </c>
       <c r="AJ2">
-        <v>0.09486167429398595</v>
+        <v>-0.1384885929330113</v>
       </c>
       <c r="AK2">
-        <v>0.09071056667881781</v>
+        <v>-0.2408494813074966</v>
       </c>
       <c r="AL2">
-        <v>8.357999999999999</v>
+        <v>4.237</v>
       </c>
       <c r="AM2">
-        <v>5.595999999999998</v>
+        <v>-1.351</v>
       </c>
       <c r="AN2">
-        <v>11.5868587778459</v>
+        <v>1.588123011664899</v>
       </c>
       <c r="AO2">
-        <v>0.7233787987556832</v>
+        <v>4.16757139485485</v>
       </c>
       <c r="AP2">
-        <v>5.390762313509095</v>
+        <v>-1.565853658536585</v>
       </c>
       <c r="AQ2">
-        <v>1.080414581844175</v>
+        <v>-13.07031828275352</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unfold.vc ASI S.A. (WSE:UNF)</t>
+          <t>Baltic Bridge Spólka Akcyjna (WSE:WIS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,100 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.124</v>
+        <v>0.255</v>
       </c>
       <c r="G3">
-        <v>1.423312883435583</v>
+        <v>-0.3142857142857142</v>
       </c>
       <c r="H3">
-        <v>1.423312883435583</v>
+        <v>-0.3142857142857142</v>
       </c>
       <c r="I3">
-        <v>0.9325153374233128</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="J3">
-        <v>0.9325153374233128</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="K3">
-        <v>5.37</v>
+        <v>0.011</v>
       </c>
       <c r="L3">
-        <v>0.6588957055214724</v>
+        <v>0.1571428571428571</v>
       </c>
       <c r="M3">
-        <v>0.663</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.03745762711864407</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.123463687150838</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.663</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03745762711864407</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.123463687150838</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>2.15</v>
+        <v>0.008</v>
       </c>
       <c r="V3">
-        <v>0.1214689265536723</v>
+        <v>0.003174603174603175</v>
       </c>
       <c r="W3">
-        <v>0.3420382165605096</v>
+        <v>-0.01368159203980099</v>
       </c>
       <c r="X3">
-        <v>0.08082114696334053</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="Y3">
-        <v>0.2612170695971691</v>
-      </c>
-      <c r="Z3">
-        <v>0.5892986261749821</v>
-      </c>
-      <c r="AA3">
-        <v>0.549530007230658</v>
+        <v>-0.08231488243152288</v>
       </c>
       <c r="AB3">
-        <v>0.08077553554787026</v>
-      </c>
-      <c r="AC3">
-        <v>0.4687544716827878</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="AD3">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.121</v>
+        <v>-0.008</v>
       </c>
       <c r="AH3">
-        <v>0.001635738056291951</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.001673495296901148</v>
+        <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1361448103215868</v>
+        <v>-0.003184713375796179</v>
       </c>
       <c r="AK3">
-        <v>-0.1397325251992885</v>
+        <v>0.008810572687224669</v>
       </c>
       <c r="AL3">
-        <v>0.062</v>
+        <v>0.015</v>
       </c>
       <c r="AM3">
-        <v>-0.192</v>
-      </c>
-      <c r="AN3">
-        <v>0.003810775295663601</v>
+        <v>0.015</v>
       </c>
       <c r="AO3">
-        <v>122.5806451612903</v>
-      </c>
-      <c r="AP3">
-        <v>-0.2787122207621551</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="AQ3">
-        <v>-39.58333333333333</v>
+        <v>2.533333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Foto Volt Eko Energia S.A. (WSE:FVE)</t>
+          <t>Magna Polonia S.A. (WSE:06N)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -852,32 +834,38 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.0113</v>
+      </c>
+      <c r="E4">
+        <v>1.014</v>
+      </c>
       <c r="G4">
-        <v>0.1611650485436893</v>
+        <v>0.8180645161290322</v>
       </c>
       <c r="H4">
-        <v>0.1611650485436893</v>
+        <v>0.7483870967741935</v>
       </c>
       <c r="I4">
-        <v>0.08058252427184466</v>
+        <v>13.67741935483871</v>
       </c>
       <c r="J4">
-        <v>0.07363575493806496</v>
+        <v>11.1687469606095</v>
       </c>
       <c r="K4">
-        <v>0.053</v>
+        <v>16.3</v>
       </c>
       <c r="L4">
-        <v>0.05145631067961165</v>
+        <v>10.51612903225806</v>
       </c>
       <c r="M4">
-        <v>0.002</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.001098901098901099</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.03773584905660377</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -889,73 +877,76 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0.002</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>0.089</v>
+        <v>13.8</v>
       </c>
       <c r="V4">
-        <v>0.04890109890109889</v>
+        <v>1.045454545454546</v>
       </c>
       <c r="W4">
-        <v>0.2030651340996169</v>
+        <v>2.974452554744525</v>
       </c>
       <c r="X4">
-        <v>0.08089619235639051</v>
+        <v>0.06904885456629203</v>
       </c>
       <c r="Y4">
-        <v>0.1221689417432263</v>
+        <v>2.905403700178233</v>
       </c>
       <c r="Z4">
-        <v>3.759124087591241</v>
+        <v>0.2593708165997323</v>
       </c>
       <c r="AA4">
-        <v>0.2768059400956456</v>
+        <v>2.896847019569063</v>
       </c>
       <c r="AB4">
-        <v>0.08078906841646831</v>
+        <v>0.0687041577758488</v>
       </c>
       <c r="AC4">
-        <v>0.1960168716791773</v>
+        <v>2.828142861793214</v>
       </c>
       <c r="AD4">
-        <v>0.007</v>
+        <v>0.227</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.007</v>
+        <v>0.227</v>
       </c>
       <c r="AG4">
-        <v>-0.08199999999999999</v>
+        <v>-13.573</v>
       </c>
       <c r="AH4">
-        <v>0.003831417624521073</v>
+        <v>0.0169062337081999</v>
       </c>
       <c r="AI4">
-        <v>0.02966101694915254</v>
+        <v>0.009944364130196696</v>
       </c>
       <c r="AJ4">
-        <v>-0.04718066743383199</v>
+        <v>36.38873994638059</v>
       </c>
       <c r="AK4">
-        <v>-0.5578231292517005</v>
+        <v>-1.503600310180569</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.745</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.02200000000000002</v>
       </c>
       <c r="AN4">
-        <v>0.07865168539325844</v>
+        <v>0.01070754716981132</v>
+      </c>
+      <c r="AO4">
+        <v>28.45637583892617</v>
       </c>
       <c r="AP4">
-        <v>-0.9213483146067415</v>
+        <v>-0.6402358490566038</v>
+      </c>
+      <c r="AQ4">
+        <v>963.6363636363627</v>
       </c>
     </row>
     <row r="5">
@@ -975,121 +966,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.00625</v>
-      </c>
-      <c r="E5">
-        <v>-0.0607</v>
+        <v>-0.0239</v>
       </c>
       <c r="G5">
-        <v>0.3136563876651983</v>
+        <v>0.1748792270531401</v>
       </c>
       <c r="H5">
-        <v>0.3136563876651983</v>
+        <v>0.1748792270531401</v>
       </c>
       <c r="I5">
-        <v>0.2356828193832599</v>
+        <v>0.1502415458937198</v>
       </c>
       <c r="J5">
-        <v>0.193499851710394</v>
+        <v>0.1216758835494533</v>
       </c>
       <c r="K5">
-        <v>4.93</v>
+        <v>3.54</v>
       </c>
       <c r="L5">
-        <v>0.2171806167400881</v>
+        <v>0.1710144927536232</v>
       </c>
       <c r="M5">
-        <v>4.57</v>
+        <v>3.002</v>
       </c>
       <c r="N5">
-        <v>0.1106537530266344</v>
+        <v>0.03853658536585366</v>
       </c>
       <c r="O5">
-        <v>0.9269776876267749</v>
+        <v>0.8480225988700566</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.172</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.00220795892169448</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.04858757062146892</v>
       </c>
       <c r="S5">
-        <v>4.57</v>
+        <v>2.83</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.9427048634243836</v>
       </c>
       <c r="U5">
-        <v>15.1</v>
+        <v>11.3</v>
       </c>
       <c r="V5">
-        <v>0.3656174334140436</v>
+        <v>0.1450577663671374</v>
       </c>
       <c r="W5">
-        <v>0.2581151832460732</v>
+        <v>0.2254777070063694</v>
       </c>
       <c r="X5">
-        <v>0.08099755428631714</v>
+        <v>0.06899933222684908</v>
       </c>
       <c r="Y5">
-        <v>0.1771176289597561</v>
+        <v>0.1564783747795204</v>
       </c>
       <c r="Z5">
-        <v>1.374008837237455</v>
+        <v>23.46938775510205</v>
       </c>
       <c r="AA5">
-        <v>0.2658705062542185</v>
+        <v>2.855658491466763</v>
       </c>
       <c r="AB5">
-        <v>0.08076495474107177</v>
+        <v>0.06862559189387958</v>
       </c>
       <c r="AC5">
-        <v>0.1851055515131468</v>
+        <v>2.787032899572883</v>
       </c>
       <c r="AD5">
-        <v>0.282</v>
+        <v>1.18</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.282</v>
+        <v>1.18</v>
       </c>
       <c r="AG5">
-        <v>-14.818</v>
+        <v>-10.12</v>
       </c>
       <c r="AH5">
-        <v>0.00678178057813477</v>
+        <v>0.01492159838138593</v>
       </c>
       <c r="AI5">
-        <v>0.01660581792486162</v>
+        <v>0.05678537054860442</v>
       </c>
       <c r="AJ5">
-        <v>-0.559549882939355</v>
+        <v>-0.1493065801121275</v>
       </c>
       <c r="AK5">
-        <v>-7.87353878852285</v>
+        <v>-1.067510548523207</v>
       </c>
       <c r="AL5">
-        <v>0.027</v>
+        <v>0.047</v>
       </c>
       <c r="AM5">
-        <v>-0.293</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="AN5">
-        <v>0.04723618090452261</v>
+        <v>0.3470588235294118</v>
       </c>
       <c r="AO5">
-        <v>198.1481481481481</v>
+        <v>66.17021276595744</v>
       </c>
       <c r="AP5">
-        <v>-2.482077051926298</v>
+        <v>-2.976470588235295</v>
       </c>
       <c r="AQ5">
-        <v>-18.25938566552901</v>
+        <v>-4.712121212121213</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erato Energy S.A. (WSE:ERA)</t>
+          <t>Foto Volt Eko Energia S.A. (WSE:FVE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,37 +1097,34 @@
         </is>
       </c>
       <c r="D6">
-        <v>1.238</v>
-      </c>
-      <c r="E6">
-        <v>-0.229</v>
+        <v>0.257</v>
       </c>
       <c r="G6">
-        <v>0.07361111111111111</v>
+        <v>0.08461538461538461</v>
       </c>
       <c r="H6">
-        <v>0.07361111111111111</v>
+        <v>0.08461538461538461</v>
       </c>
       <c r="I6">
-        <v>0.02759259259259259</v>
+        <v>0.02403846153846154</v>
       </c>
       <c r="J6">
-        <v>0.01379629629629629</v>
+        <v>0.02403846153846154</v>
       </c>
       <c r="K6">
-        <v>0.192</v>
+        <v>-0.02</v>
       </c>
       <c r="L6">
-        <v>0.008888888888888889</v>
+        <v>-0.01923076923076923</v>
       </c>
       <c r="M6">
-        <v>0.081</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.004402173913043479</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.421875</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1148,82 +1133,79 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0.081</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.009945652173913045</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.006736842105263158</v>
+        <v>-0.08733624454148471</v>
       </c>
       <c r="X6">
-        <v>0.08401686420629012</v>
+        <v>0.07057329464156105</v>
       </c>
       <c r="Y6">
-        <v>-0.07728002210102697</v>
+        <v>-0.1579095391830458</v>
       </c>
       <c r="Z6">
-        <v>8.473911337779523</v>
+        <v>16.77419354838709</v>
       </c>
       <c r="AA6">
-        <v>0.1169085916045508</v>
+        <v>0.4032258064516128</v>
       </c>
       <c r="AB6">
-        <v>0.0813035291121193</v>
+        <v>0.06894480543632216</v>
       </c>
       <c r="AC6">
-        <v>0.03560506249243152</v>
+        <v>0.3342810010152907</v>
       </c>
       <c r="AD6">
-        <v>1.76</v>
+        <v>0.114</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.76</v>
+        <v>0.114</v>
       </c>
       <c r="AG6">
-        <v>1.577</v>
+        <v>0.114</v>
       </c>
       <c r="AH6">
-        <v>0.0873015873015873</v>
+        <v>0.0743155149934811</v>
       </c>
       <c r="AI6">
-        <v>0.4433249370277079</v>
+        <v>0.3220338983050848</v>
       </c>
       <c r="AJ6">
-        <v>0.07894078189918408</v>
+        <v>0.0743155149934811</v>
       </c>
       <c r="AK6">
-        <v>0.4164246105096382</v>
+        <v>0.3220338983050848</v>
       </c>
       <c r="AL6">
-        <v>0.059</v>
+        <v>0.004</v>
       </c>
       <c r="AM6">
-        <v>0.059</v>
+        <v>0.004</v>
       </c>
       <c r="AN6">
-        <v>1.257142857142857</v>
+        <v>1.9</v>
       </c>
       <c r="AO6">
-        <v>10.10169491525424</v>
+        <v>6.25</v>
       </c>
       <c r="AP6">
-        <v>1.126428571428572</v>
+        <v>1.9</v>
       </c>
       <c r="AQ6">
-        <v>10.10169491525424</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -1243,46 +1225,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.341</v>
+        <v>-0.32</v>
       </c>
       <c r="E7">
-        <v>-0.468</v>
+        <v>-0.279</v>
       </c>
       <c r="G7">
-        <v>0.3644444444444444</v>
+        <v>0.2194690265486726</v>
       </c>
       <c r="H7">
-        <v>0.3644444444444444</v>
+        <v>0.2194690265486726</v>
       </c>
       <c r="I7">
-        <v>0.1966666666666667</v>
+        <v>0.1858407079646018</v>
       </c>
       <c r="J7">
-        <v>0.1508282051282051</v>
+        <v>0.1457057080627122</v>
       </c>
       <c r="K7">
-        <v>0.847</v>
+        <v>2.96</v>
       </c>
       <c r="L7">
-        <v>0.0941111111111111</v>
+        <v>0.2619469026548673</v>
       </c>
       <c r="M7">
-        <v>0.269</v>
+        <v>0.233</v>
       </c>
       <c r="N7">
-        <v>0.01805369127516778</v>
+        <v>0.009748953974895398</v>
       </c>
       <c r="O7">
-        <v>0.3175914994096812</v>
+        <v>0.07871621621621622</v>
       </c>
       <c r="P7">
-        <v>0.269</v>
+        <v>0.233</v>
       </c>
       <c r="Q7">
-        <v>0.01805369127516778</v>
+        <v>0.009748953974895398</v>
       </c>
       <c r="R7">
-        <v>0.3175914994096812</v>
+        <v>0.07871621621621622</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1291,73 +1273,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2.46</v>
+        <v>2.65</v>
       </c>
       <c r="V7">
-        <v>0.1651006711409396</v>
+        <v>0.1108786610878661</v>
       </c>
       <c r="W7">
-        <v>0.03184210526315789</v>
+        <v>0.1351598173515982</v>
       </c>
       <c r="X7">
-        <v>0.0809342732434282</v>
+        <v>0.06932588458309624</v>
       </c>
       <c r="Y7">
-        <v>-0.0490921679802703</v>
+        <v>0.06583393276850194</v>
       </c>
       <c r="Z7">
-        <v>0.3560830860534124</v>
+        <v>0.57907143589218</v>
       </c>
       <c r="AA7">
-        <v>0.05370737274594841</v>
+        <v>0.08437401358556153</v>
       </c>
       <c r="AB7">
-        <v>0.08079591276785066</v>
+        <v>0.06875008421969271</v>
       </c>
       <c r="AC7">
-        <v>-0.02708854002190225</v>
+        <v>0.01562392936586882</v>
       </c>
       <c r="AD7">
-        <v>0.074</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.074</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AG7">
-        <v>-2.386</v>
+        <v>-1.965</v>
       </c>
       <c r="AH7">
-        <v>0.004941899292106317</v>
+        <v>0.02786251779540371</v>
       </c>
       <c r="AI7">
-        <v>0.002999108373186349</v>
+        <v>0.02148345617061314</v>
       </c>
       <c r="AJ7">
-        <v>-0.1906664535719994</v>
+        <v>-0.08958285844540688</v>
       </c>
       <c r="AK7">
-        <v>-0.1074097416043936</v>
+        <v>-0.06721395587480759</v>
       </c>
       <c r="AL7">
-        <v>0.027</v>
+        <v>0.042</v>
       </c>
       <c r="AM7">
-        <v>-0.141</v>
+        <v>-1.298</v>
       </c>
       <c r="AN7">
-        <v>0.04065934065934065</v>
+        <v>0.3127853881278539</v>
       </c>
       <c r="AO7">
-        <v>65.55555555555556</v>
+        <v>50</v>
       </c>
       <c r="AP7">
-        <v>-1.310989010989011</v>
+        <v>-0.8972602739726027</v>
       </c>
       <c r="AQ7">
-        <v>-12.5531914893617</v>
+        <v>-1.617873651771957</v>
       </c>
     </row>
     <row r="8">
@@ -1368,7 +1350,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Starhedge S.A. (WSE:SHG)</t>
+          <t>Caspar Asset Management S.A. (WSE:CSR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1377,121 +1359,112 @@
         </is>
       </c>
       <c r="D8">
-        <v>1.485</v>
+        <v>0.144</v>
       </c>
       <c r="E8">
-        <v>0.00045</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="G8">
-        <v>0.1237864077669903</v>
+        <v>0.0001383125864453665</v>
       </c>
       <c r="H8">
-        <v>0.1237864077669903</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.07487864077669902</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.07487864077669902</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>0.509</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="L8">
-        <v>0.06177184466019418</v>
+        <v>0.0946058091286307</v>
       </c>
       <c r="M8">
-        <v>0.029</v>
+        <v>1.26</v>
       </c>
       <c r="N8">
-        <v>0.003629536921151439</v>
+        <v>0.05833333333333333</v>
       </c>
       <c r="O8">
-        <v>0.05697445972495089</v>
+        <v>1.842105263157895</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.05833333333333333</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>1.842105263157895</v>
       </c>
       <c r="S8">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>0.127</v>
+        <v>1.44</v>
       </c>
       <c r="V8">
-        <v>0.01589486858573216</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="W8">
-        <v>0.04669724770642202</v>
+        <v>0.1572413793103448</v>
       </c>
       <c r="X8">
-        <v>0.08638115635932486</v>
+        <v>0.06988628858817421</v>
       </c>
       <c r="Y8">
-        <v>-0.03968390865290285</v>
+        <v>0.08735509072217064</v>
       </c>
       <c r="Z8">
-        <v>0.6163051608077785</v>
+        <v>1.785185185185186</v>
       </c>
       <c r="AA8">
-        <v>0.04614809274495138</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.08163932045536477</v>
+        <v>0.06883992793489695</v>
       </c>
       <c r="AC8">
-        <v>-0.03549122771041339</v>
+        <v>-0.06883992793489695</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="AG8">
-        <v>1.193</v>
+        <v>-0.3199999999999998</v>
       </c>
       <c r="AH8">
-        <v>0.1417830290010741</v>
+        <v>0.04929577464788732</v>
       </c>
       <c r="AI8">
-        <v>0.09482758620689656</v>
+        <v>0.2014388489208633</v>
       </c>
       <c r="AJ8">
-        <v>0.1299139714690188</v>
+        <v>-0.0150375939849624</v>
       </c>
       <c r="AK8">
-        <v>0.08649314869861525</v>
+        <v>-0.0776699029126213</v>
       </c>
       <c r="AL8">
-        <v>0.206</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.143</v>
-      </c>
-      <c r="AN8">
-        <v>1.517241379310345</v>
-      </c>
-      <c r="AO8">
-        <v>2.995145631067961</v>
-      </c>
-      <c r="AP8">
-        <v>1.371264367816092</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="AQ8">
-        <v>4.314685314685315</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1475,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nexity Global S.A. (WSE:NXG)</t>
+          <t>Capital Partners S.A. (WSE:CPA)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1511,25 +1484,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.06509999999999999</v>
+        <v>-0.368</v>
       </c>
       <c r="G9">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>-13.75</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.4625</v>
+        <v>-0.04761904761904762</v>
       </c>
       <c r="J9">
-        <v>0.4625</v>
+        <v>-0.02380952380952381</v>
       </c>
       <c r="K9">
-        <v>-0.098</v>
+        <v>0.005</v>
       </c>
       <c r="L9">
-        <v>-1.225</v>
+        <v>0.02380952380952381</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1538,7 +1511,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1547,79 +1520,70 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.06900000000000001</v>
+        <v>0.477</v>
       </c>
       <c r="V9">
-        <v>0.01095238095238095</v>
+        <v>0.2315533980582524</v>
       </c>
       <c r="W9">
-        <v>-0.8448275862068966</v>
+        <v>0.003448275862068966</v>
       </c>
       <c r="X9">
-        <v>0.08139673415401688</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="Y9">
-        <v>-0.9262243203609135</v>
+        <v>-0.06518501452965292</v>
       </c>
       <c r="Z9">
-        <v>0.07662835249042145</v>
+        <v>0.1515151515151515</v>
       </c>
       <c r="AA9">
-        <v>0.03544061302681992</v>
+        <v>-0.003607503607503608</v>
       </c>
       <c r="AB9">
-        <v>0.08093395074374317</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="AC9">
-        <v>-0.04549333771692325</v>
+        <v>-0.07224079399922551</v>
       </c>
       <c r="AD9">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.117</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>0.048</v>
+        <v>-0.477</v>
       </c>
       <c r="AH9">
-        <v>0.0182328190743338</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>-23.40000000000004</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.007561436672967864</v>
+        <v>-0.3013265950726468</v>
       </c>
       <c r="AK9">
-        <v>-0.6486486486486487</v>
+        <v>-0.4066496163682864</v>
       </c>
       <c r="AL9">
-        <v>0.038</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>-0.059</v>
-      </c>
-      <c r="AN9">
-        <v>1.647887323943662</v>
-      </c>
-      <c r="AO9">
-        <v>0.9736842105263158</v>
-      </c>
-      <c r="AP9">
-        <v>0.6760563380281691</v>
+        <v>-0.023</v>
       </c>
       <c r="AQ9">
-        <v>-0.6271186440677965</v>
+        <v>0.4347826086956522</v>
       </c>
     </row>
     <row r="10">
@@ -1630,7 +1594,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MCI Capital Alternatywna Spólka Inwestycyjna S.A. (WSE:MCI)</t>
+          <t>Black Pearl S.A. (WSE:BPC)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1639,121 +1603,106 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.009889999999999999</v>
-      </c>
-      <c r="E10">
-        <v>-0.145</v>
+        <v>-0.675</v>
       </c>
       <c r="G10">
-        <v>8.567307692307692</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>8.567307692307692</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.07134615384615384</v>
+        <v>-5.142857142857142</v>
       </c>
       <c r="J10">
-        <v>0.07134615384615384</v>
+        <v>-5.142857142857142</v>
       </c>
       <c r="K10">
-        <v>3.69</v>
+        <v>-3.62</v>
       </c>
       <c r="L10">
-        <v>0.3548076923076923</v>
+        <v>-517.1428571428571</v>
       </c>
       <c r="M10">
-        <v>7.550499999999999</v>
+        <v>0.003</v>
       </c>
       <c r="N10">
-        <v>0.04011955366631243</v>
+        <v>0.0002419354838709677</v>
       </c>
       <c r="O10">
-        <v>2.04620596205962</v>
+        <v>-0.0008287292817679558</v>
       </c>
       <c r="P10">
-        <v>7.261499999999999</v>
+        <v>0.003</v>
       </c>
       <c r="Q10">
-        <v>0.03858395324123273</v>
+        <v>0.0002419354838709677</v>
       </c>
       <c r="R10">
-        <v>1.967886178861788</v>
+        <v>-0.0008287292817679558</v>
       </c>
       <c r="S10">
-        <v>0.2889999999999997</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.03827561088669621</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>7.77</v>
+        <v>0.011</v>
       </c>
       <c r="V10">
-        <v>0.04128586609989373</v>
+        <v>0.0008870967741935483</v>
       </c>
       <c r="W10">
-        <v>0.008026974113552316</v>
+        <v>-0.8098434004474273</v>
       </c>
       <c r="X10">
-        <v>0.08957953703056024</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="Y10">
-        <v>-0.08155256291700792</v>
+        <v>-0.8784766908391493</v>
       </c>
       <c r="Z10">
-        <v>0.02044627936695173</v>
+        <v>0.001565995525727069</v>
       </c>
       <c r="AA10">
-        <v>0.001458763393295979</v>
+        <v>-0.008053691275167784</v>
       </c>
       <c r="AB10">
-        <v>0.08075030066726693</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="AC10">
-        <v>-0.07929153727397095</v>
+        <v>-0.07668698166688967</v>
       </c>
       <c r="AD10">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>48.8</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>41.03</v>
+        <v>-0.011</v>
       </c>
       <c r="AH10">
-        <v>0.2059071729957806</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.1164677804295943</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0.1789905335252803</v>
+        <v>-0.0008878844135927031</v>
       </c>
       <c r="AK10">
-        <v>0.09977384918415486</v>
+        <v>-0.008215085884988796</v>
       </c>
       <c r="AL10">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.188</v>
-      </c>
-      <c r="AN10">
-        <v>57.68321513002364</v>
-      </c>
-      <c r="AO10">
-        <v>0.1705747126436782</v>
-      </c>
-      <c r="AP10">
-        <v>48.49881796690308</v>
-      </c>
-      <c r="AQ10">
-        <v>0.1771728748806113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1764,7 +1713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caspar Asset Management S.A. (WSE:CSR)</t>
+          <t>BBI Development S.A. (WSE:BBD)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1773,112 +1722,118 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.25</v>
-      </c>
-      <c r="E11">
-        <v>0.234</v>
+        <v>0.249</v>
       </c>
       <c r="G11">
-        <v>0.0001358695652173913</v>
+        <v>-0.08440545808966862</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-0.08440545808966862</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>-0.5497076023391813</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>-0.5423910037791502</v>
       </c>
       <c r="K11">
-        <v>1.02</v>
+        <v>5.64</v>
       </c>
       <c r="L11">
-        <v>0.1385869565217391</v>
+        <v>1.099415204678363</v>
       </c>
       <c r="M11">
-        <v>1.35</v>
+        <v>0.06</v>
       </c>
       <c r="N11">
-        <v>0.04166666666666667</v>
+        <v>0.005172413793103448</v>
       </c>
       <c r="O11">
-        <v>1.323529411764706</v>
+        <v>0.01063829787234043</v>
       </c>
       <c r="P11">
-        <v>1.35</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.04166666666666667</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>1.323529411764706</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="V11">
-        <v>0.04444444444444445</v>
+        <v>0.1448275862068966</v>
       </c>
       <c r="W11">
-        <v>0.166394779771615</v>
+        <v>0.2311475409836066</v>
       </c>
       <c r="X11">
-        <v>0.08196146926123379</v>
+        <v>0.09904781557900663</v>
       </c>
       <c r="Y11">
-        <v>0.08443331051038122</v>
+        <v>0.1320997254045999</v>
       </c>
       <c r="Z11">
-        <v>1.84971098265896</v>
+        <v>0.1644230769230769</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>-0.08918159773676412</v>
       </c>
       <c r="AB11">
-        <v>0.08097494353803845</v>
+        <v>0.07096917345884574</v>
       </c>
       <c r="AC11">
-        <v>-0.08097494353803845</v>
+        <v>-0.1601507711956099</v>
       </c>
       <c r="AD11">
-        <v>1.14</v>
+        <v>14.6</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>1.14</v>
+        <v>14.6</v>
       </c>
       <c r="AG11">
-        <v>-0.3</v>
+        <v>12.92</v>
       </c>
       <c r="AH11">
-        <v>0.03398926654740608</v>
+        <v>0.5572519083969466</v>
       </c>
       <c r="AI11">
-        <v>0.2072727272727272</v>
+        <v>0.305439330543933</v>
       </c>
       <c r="AJ11">
-        <v>-0.009345794392523366</v>
+        <v>0.5269168026101142</v>
       </c>
       <c r="AK11">
-        <v>-0.07389162561576355</v>
+        <v>0.2801387684301821</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM11">
-        <v>-0.073</v>
+        <v>1.173</v>
+      </c>
+      <c r="AN11">
+        <v>-5.910931174089068</v>
+      </c>
+      <c r="AO11">
+        <v>-1.611428571428571</v>
+      </c>
+      <c r="AP11">
+        <v>-5.23076923076923</v>
       </c>
       <c r="AQ11">
-        <v>-0</v>
+        <v>-2.404092071611253</v>
       </c>
     </row>
     <row r="12">
@@ -1889,7 +1844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Invista S.A. (WSE:NTC)</t>
+          <t>Adiuvo Investments S.A. (WSE:ADV)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1898,28 +1853,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.302</v>
-      </c>
-      <c r="E12">
-        <v>-0.442</v>
+        <v>-0.452</v>
       </c>
       <c r="G12">
-        <v>-0.03798449612403101</v>
+        <v>221.6666666666667</v>
       </c>
       <c r="H12">
-        <v>-0.03798449612403101</v>
+        <v>-65.33333333333333</v>
       </c>
       <c r="I12">
-        <v>0.01472868217054264</v>
+        <v>-23.66666666666667</v>
       </c>
       <c r="J12">
-        <v>0.01472868217054264</v>
+        <v>-23.66666666666667</v>
       </c>
       <c r="K12">
-        <v>0.028</v>
+        <v>-11.4</v>
       </c>
       <c r="L12">
-        <v>0.02170542635658915</v>
+        <v>-380</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1928,7 +1880,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1937,73 +1889,79 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.015</v>
+        <v>0.052</v>
       </c>
       <c r="V12">
-        <v>0.005725190839694656</v>
+        <v>0.0174496644295302</v>
       </c>
       <c r="W12">
-        <v>0.007235142118863049</v>
+        <v>7.354838709677419</v>
       </c>
       <c r="X12">
-        <v>0.08330836812090016</v>
+        <v>0.1442096245612477</v>
       </c>
       <c r="Y12">
-        <v>-0.07607322600203711</v>
+        <v>7.210629085116171</v>
       </c>
       <c r="Z12">
-        <v>0.316719862509207</v>
+        <v>0.005047106325706594</v>
       </c>
       <c r="AA12">
-        <v>0.004664866191996072</v>
+        <v>-0.1194481830417227</v>
       </c>
       <c r="AB12">
-        <v>0.08680403618890309</v>
+        <v>0.07796179974990528</v>
       </c>
       <c r="AC12">
-        <v>-0.08213916999690701</v>
+        <v>-0.197409982791628</v>
       </c>
       <c r="AD12">
-        <v>0.196</v>
+        <v>9.32</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.196</v>
+        <v>9.32</v>
       </c>
       <c r="AG12">
-        <v>0.181</v>
+        <v>9.268000000000001</v>
       </c>
       <c r="AH12">
-        <v>0.06960227272727272</v>
+        <v>0.7577235772357723</v>
       </c>
       <c r="AI12">
-        <v>0.05892964521948287</v>
+        <v>-2.757396449704143</v>
       </c>
       <c r="AJ12">
-        <v>0.06461977865048196</v>
+        <v>0.7566949706074461</v>
       </c>
       <c r="AK12">
-        <v>0.05466626396858955</v>
+        <v>-2.700466200466202</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1.306</v>
       </c>
       <c r="AN12">
-        <v>8.166666666666666</v>
+        <v>-12.31175693527081</v>
+      </c>
+      <c r="AO12">
+        <v>-0.5338345864661653</v>
       </c>
       <c r="AP12">
-        <v>7.541666666666666</v>
+        <v>-12.24306472919419</v>
+      </c>
+      <c r="AQ12">
+        <v>-0.5436447166921898</v>
       </c>
     </row>
     <row r="13">
@@ -2014,7 +1972,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BBI Development S.A. (WSE:BBD)</t>
+          <t>Skarbiec Holding S.A. (WSE:SKH)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2023,34 +1981,34 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.212</v>
+        <v>-0.109</v>
       </c>
       <c r="G13">
-        <v>-0.139067055393586</v>
+        <v>-0.2346153846153846</v>
       </c>
       <c r="H13">
-        <v>-0.139067055393586</v>
+        <v>-0.2346153846153846</v>
       </c>
       <c r="I13">
-        <v>-0.04198250728862973</v>
+        <v>-0.2238461538461539</v>
       </c>
       <c r="J13">
-        <v>-0.04198250728862973</v>
+        <v>-0.2238461538461539</v>
       </c>
       <c r="K13">
-        <v>-1.18</v>
+        <v>-4.83</v>
       </c>
       <c r="L13">
-        <v>-0.3440233236151603</v>
+        <v>-0.3715384615384615</v>
       </c>
       <c r="M13">
-        <v>0.018</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.002031602708803612</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>-0.01525423728813559</v>
+        <v>0</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -2062,79 +2020,76 @@
         <v>0</v>
       </c>
       <c r="S13">
-        <v>0.018</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.26</v>
+        <v>21.6</v>
       </c>
       <c r="V13">
-        <v>0.255079006772009</v>
+        <v>0.4886877828054298</v>
       </c>
       <c r="W13">
-        <v>-0.03699059561128527</v>
+        <v>-0.1085393258426966</v>
       </c>
       <c r="X13">
-        <v>0.1340937884366396</v>
+        <v>0.06891813081883072</v>
       </c>
       <c r="Y13">
-        <v>-0.1710843840479249</v>
+        <v>-0.1774574566615273</v>
       </c>
       <c r="Z13">
-        <v>0.08000933053417308</v>
+        <v>0.7447722715554281</v>
       </c>
       <c r="AA13">
-        <v>-0.003358992302309307</v>
+        <v>-0.1667144084789459</v>
       </c>
       <c r="AB13">
-        <v>0.08452957371084002</v>
+        <v>0.06862727980506614</v>
       </c>
       <c r="AC13">
-        <v>-0.08788856601314933</v>
+        <v>-0.235341688284012</v>
       </c>
       <c r="AD13">
-        <v>13.9</v>
+        <v>0.521</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>13.9</v>
+        <v>0.521</v>
       </c>
       <c r="AG13">
-        <v>11.64</v>
+        <v>-21.079</v>
       </c>
       <c r="AH13">
-        <v>0.6107205623901583</v>
+        <v>0.01165000782630084</v>
       </c>
       <c r="AI13">
-        <v>0.3629242819843342</v>
+        <v>0.01279438127747354</v>
       </c>
       <c r="AJ13">
-        <v>0.5678048780487805</v>
+        <v>-0.9116820206738462</v>
       </c>
       <c r="AK13">
-        <v>0.3229744728079911</v>
+        <v>-1.102400502065791</v>
       </c>
       <c r="AL13">
-        <v>1.74</v>
+        <v>0.02</v>
       </c>
       <c r="AM13">
-        <v>1.075</v>
+        <v>-1.79</v>
       </c>
       <c r="AN13">
-        <v>-127.5229357798165</v>
+        <v>-0.1936802973977695</v>
       </c>
       <c r="AO13">
-        <v>-0.08275862068965517</v>
+        <v>-145.5</v>
       </c>
       <c r="AP13">
-        <v>-106.7889908256881</v>
+        <v>7.836059479553904</v>
       </c>
       <c r="AQ13">
-        <v>-0.133953488372093</v>
+        <v>1.625698324022346</v>
       </c>
     </row>
     <row r="14">
@@ -2145,7 +2100,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Black Pearl S.A. (WSE:BPC)</t>
+          <t>Erato Energy S.A. (WSE:ERA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2154,112 +2109,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.355</v>
+        <v>1.366</v>
       </c>
       <c r="G14">
-        <v>-24.90909090909091</v>
+        <v>-0.001515151515151515</v>
       </c>
       <c r="H14">
-        <v>-24.90909090909091</v>
+        <v>-0.001515151515151515</v>
       </c>
       <c r="I14">
-        <v>-10.36363636363637</v>
+        <v>-0.1582251082251082</v>
       </c>
       <c r="J14">
-        <v>-10.36363636363637</v>
+        <v>-0.1582251082251082</v>
       </c>
       <c r="K14">
-        <v>-0.221</v>
+        <v>-0.947</v>
       </c>
       <c r="L14">
-        <v>-20.09090909090909</v>
+        <v>-0.204978354978355</v>
       </c>
       <c r="M14">
-        <v>8.094900000000001</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.6040970149253732</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>-36.62850678733032</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>8.094900000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.6040970149253732</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>-36.62850678733032</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>0.011</v>
+        <v>0.237</v>
       </c>
       <c r="V14">
-        <v>0.0008208955223880597</v>
+        <v>0.0156953642384106</v>
       </c>
       <c r="W14">
-        <v>-0.03587662337662337</v>
+        <v>-0.4285067873303167</v>
       </c>
       <c r="X14">
-        <v>0.08076545382715974</v>
+        <v>0.07143386583081233</v>
       </c>
       <c r="Y14">
-        <v>-0.1166420772037831</v>
+        <v>-0.4999406531611291</v>
       </c>
       <c r="Z14">
-        <v>0.001841312353531972</v>
+        <v>1.21996303142329</v>
       </c>
       <c r="AA14">
-        <v>-0.0190826916638768</v>
+        <v>-0.1930287826775812</v>
       </c>
       <c r="AB14">
-        <v>0.08076545382715974</v>
+        <v>0.0692931681533073</v>
       </c>
       <c r="AC14">
-        <v>-0.09984814549103654</v>
+        <v>-0.2623219508308885</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14">
-        <v>-0.011</v>
+        <v>1.513</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.1038575667655786</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.6561679790026247</v>
       </c>
       <c r="AJ14">
-        <v>-0.0008215699454776307</v>
+        <v>0.0910732558839463</v>
       </c>
       <c r="AK14">
-        <v>-0.002245356195141865</v>
+        <v>0.6226337448559671</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN14">
-        <v>-0</v>
+        <v>-2.854812398042414</v>
+      </c>
+      <c r="AO14">
+        <v>-4.27485380116959</v>
       </c>
       <c r="AP14">
-        <v>0.09909909909909909</v>
+        <v>-2.468189233278956</v>
+      </c>
+      <c r="AQ14">
+        <v>-4.3</v>
       </c>
     </row>
     <row r="15">
@@ -2270,7 +2228,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Magna Polonia S.A. (WSE:06N)</t>
+          <t>Dr.Finance S.A. (WSE:DRF)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2279,34 +2237,34 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.556</v>
+        <v>-0.025</v>
       </c>
       <c r="G15">
-        <v>-0.06893939393939394</v>
+        <v>-0.0436105476673428</v>
       </c>
       <c r="H15">
-        <v>-0.1787878787878788</v>
+        <v>-0.0436105476673428</v>
       </c>
       <c r="I15">
-        <v>-0.181060606060606</v>
+        <v>-0.01419878296146045</v>
       </c>
       <c r="J15">
-        <v>-0.181060606060606</v>
+        <v>-0.01419878296146045</v>
       </c>
       <c r="K15">
-        <v>-0.189</v>
+        <v>-0.015</v>
       </c>
       <c r="L15">
-        <v>-0.1431818181818182</v>
+        <v>-0.01521298174442191</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>0.007</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.01261261261261261</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0.4666666666666667</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2318,76 +2276,73 @@
         <v>0</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>0.007</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
       </c>
       <c r="U15">
-        <v>0.105</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="V15">
-        <v>0.008677685950413223</v>
+        <v>0.1243243243243243</v>
       </c>
       <c r="W15">
-        <v>-0.02684659090909091</v>
+        <v>-0.1153846153846154</v>
       </c>
       <c r="X15">
-        <v>0.08267293977347376</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="Y15">
-        <v>-0.1095195306825647</v>
+        <v>-0.1840179057763373</v>
       </c>
       <c r="Z15">
-        <v>0.1776103336921421</v>
+        <v>18.96153846153846</v>
       </c>
       <c r="AA15">
-        <v>-0.03215823466092572</v>
+        <v>-0.2692307692307692</v>
       </c>
       <c r="AB15">
-        <v>0.08109294063384849</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="AC15">
-        <v>-0.1132511752947742</v>
+        <v>-0.3378640596224911</v>
       </c>
       <c r="AD15">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.679</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>0.5740000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="AH15">
-        <v>0.05313404804757806</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.1007567888410743</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>0.04528956919678082</v>
+        <v>-0.1419753086419753</v>
       </c>
       <c r="AK15">
-        <v>0.08652396744045826</v>
+        <v>-1.210526315789474</v>
       </c>
       <c r="AL15">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.284</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>-3.03125</v>
-      </c>
-      <c r="AO15">
-        <v>-3.918032786885246</v>
+        <v>-0</v>
       </c>
       <c r="AP15">
-        <v>-2.5625</v>
-      </c>
-      <c r="AQ15">
-        <v>0.8415492957746479</v>
+        <v>5.307692307692308</v>
       </c>
     </row>
     <row r="16">
@@ -2398,7 +2353,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Devo Energy S.A. (WSE:DEV)</t>
+          <t>M.W. Trade SA (WSE:MWT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2407,25 +2362,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.08</v>
+        <v>-0.507</v>
       </c>
       <c r="G16">
-        <v>0.05882352941176471</v>
+        <v>-1.778325123152709</v>
       </c>
       <c r="H16">
-        <v>0.05882352941176471</v>
+        <v>-1.778325123152709</v>
       </c>
       <c r="I16">
-        <v>-0.8588235294117645</v>
+        <v>-2.610837438423645</v>
       </c>
       <c r="J16">
-        <v>-0.8588235294117645</v>
+        <v>-2.610837438423645</v>
       </c>
       <c r="K16">
-        <v>-0.08599999999999999</v>
+        <v>-0.466</v>
       </c>
       <c r="L16">
-        <v>-1.011764705882353</v>
+        <v>-2.295566502463054</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2449,31 +2404,31 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.399477806788512</v>
       </c>
       <c r="W16">
-        <v>-0.06515151515151514</v>
+        <v>-0.07818791946308726</v>
       </c>
       <c r="X16">
-        <v>0.08076545382715974</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="Y16">
-        <v>-0.1459169689786749</v>
+        <v>-0.1468212098548091</v>
       </c>
       <c r="Z16">
-        <v>0.04796839729119639</v>
+        <v>0.128888888888889</v>
       </c>
       <c r="AA16">
-        <v>-0.04119638826185101</v>
+        <v>-0.3365079365079367</v>
       </c>
       <c r="AB16">
-        <v>0.08076545382715974</v>
+        <v>0.06863329039172189</v>
       </c>
       <c r="AC16">
-        <v>-0.1219618420890108</v>
+        <v>-0.4051412268996586</v>
       </c>
       <c r="AD16">
         <v>0</v>
@@ -2485,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>-5.36</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2494,28 +2449,28 @@
         <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>3.503267973856209</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>-5.104761904761906</v>
       </c>
       <c r="AL16">
-        <v>0.021</v>
+        <v>0.092</v>
       </c>
       <c r="AM16">
-        <v>0.016</v>
+        <v>-0.021</v>
       </c>
       <c r="AN16">
         <v>-0</v>
       </c>
       <c r="AO16">
-        <v>-3.476190476190476</v>
+        <v>-5.760869565217392</v>
       </c>
       <c r="AP16">
-        <v>-0</v>
+        <v>11.21338912133891</v>
       </c>
       <c r="AQ16">
-        <v>-4.5625</v>
+        <v>25.23809523809523</v>
       </c>
     </row>
     <row r="17">
@@ -2526,7 +2481,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Carpathia Capital S.A. (WSE:CRC)</t>
+          <t>Polska Grupa Militarna Spólka Akcyjna (WSE:PMG)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2534,95 +2489,110 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D17">
+        <v>0.201</v>
+      </c>
+      <c r="G17">
+        <v>-1.533333333333333</v>
+      </c>
+      <c r="H17">
+        <v>-1.533333333333333</v>
+      </c>
+      <c r="I17">
+        <v>-3.4</v>
+      </c>
+      <c r="J17">
+        <v>-3.4</v>
+      </c>
       <c r="K17">
-        <v>-1.47</v>
+        <v>-0.133</v>
+      </c>
+      <c r="L17">
+        <v>-4.433333333333334</v>
       </c>
       <c r="M17">
-        <v>0.008</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.00380952380952381</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0.0054421768707483</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>0.008</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.00380952380952381</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0.0054421768707483</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0.215</v>
+        <v>0.225</v>
       </c>
       <c r="V17">
-        <v>0.1023809523809524</v>
+        <v>0.05160550458715596</v>
       </c>
       <c r="W17">
-        <v>-0.3006134969325154</v>
+        <v>-0.7471910112359551</v>
       </c>
       <c r="X17">
-        <v>0.08138054747896928</v>
+        <v>0.06887715701318083</v>
       </c>
       <c r="Y17">
-        <v>-0.3819940444114847</v>
+        <v>-0.816068168249136</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="AA17">
-        <v>-0.04841628959276018</v>
+        <v>-0.4722222222222222</v>
       </c>
       <c r="AB17">
-        <v>0.08087499989673994</v>
+        <v>0.06869676948507071</v>
       </c>
       <c r="AC17">
-        <v>-0.1292912894895001</v>
+        <v>-0.540918991707293</v>
       </c>
       <c r="AD17">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="AG17">
-        <v>-0.177</v>
+        <v>-0.181</v>
       </c>
       <c r="AH17">
-        <v>0.01777362020579981</v>
+        <v>0.009990917347865577</v>
       </c>
       <c r="AI17">
-        <v>0.01533494753833737</v>
+        <v>0.0421455938697318</v>
       </c>
       <c r="AJ17">
-        <v>-0.09204368174726989</v>
+        <v>-0.0433117970806413</v>
       </c>
       <c r="AK17">
-        <v>-0.07821475916924436</v>
+        <v>-0.221001221001221</v>
       </c>
       <c r="AL17">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>-0.05</v>
-      </c>
-      <c r="AO17">
-        <v>-107</v>
-      </c>
-      <c r="AQ17">
-        <v>4.28</v>
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>-0.4536082474226804</v>
+      </c>
+      <c r="AP17">
+        <v>1.865979381443299</v>
       </c>
     </row>
     <row r="18">
@@ -2633,7 +2603,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centurion Finance Spólka Akcyjna (WSE:CTF)</t>
+          <t>Soho Development S.A. (WSE:SHD)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2642,7 +2612,7 @@
         </is>
       </c>
       <c r="K18">
-        <v>-0.173</v>
+        <v>-0.874</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2666,73 +2636,70 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.006</v>
+        <v>0.573</v>
       </c>
       <c r="V18">
-        <v>0.0003015075376884422</v>
+        <v>0.2264822134387352</v>
       </c>
       <c r="W18">
-        <v>-0.08480392156862744</v>
+        <v>-0.2455056179775281</v>
       </c>
       <c r="X18">
-        <v>0.08076545382715974</v>
+        <v>0.06864284176137299</v>
       </c>
       <c r="Y18">
-        <v>-0.1655693753957872</v>
+        <v>-0.3141484597389011</v>
       </c>
       <c r="Z18">
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>-0.06053149606299212</v>
+        <v>-2</v>
       </c>
       <c r="AB18">
-        <v>0.08076545382715974</v>
+        <v>0.06863580073552336</v>
       </c>
       <c r="AC18">
-        <v>-0.1412969498901519</v>
+        <v>-2.068635800735524</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AG18">
-        <v>-0.006</v>
+        <v>-0.572</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>0.0003951007506914263</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>0.0003095017022593624</v>
       </c>
       <c r="AJ18">
-        <v>-0.0003015984719010757</v>
+        <v>-0.2921348314606741</v>
       </c>
       <c r="AK18">
-        <v>-0.00352112676056338</v>
+        <v>-0.2151993980436418</v>
       </c>
       <c r="AL18">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>-0.004999999999999999</v>
+        <v>-0.185</v>
       </c>
       <c r="AN18">
-        <v>-0</v>
-      </c>
-      <c r="AO18">
-        <v>-15.375</v>
+        <v>-0.001146788990825688</v>
       </c>
       <c r="AP18">
-        <v>0.04918032786885246</v>
+        <v>0.6559633027522935</v>
       </c>
       <c r="AQ18">
-        <v>24.6</v>
+        <v>4.713513513513513</v>
       </c>
     </row>
     <row r="19">
@@ -2743,7 +2710,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FinTech Ventures S.A. (WSE:FIV)</t>
+          <t>Agencja Rozwoju Innowacji Spólka Akcyjna (WSE:ARI)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2751,23 +2718,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D19">
+        <v>-0.258</v>
+      </c>
       <c r="G19">
-        <v>-14.95726495726496</v>
+        <v>-1.4</v>
       </c>
       <c r="H19">
-        <v>-14.95726495726496</v>
+        <v>-1.4</v>
       </c>
       <c r="I19">
-        <v>-10.68376068376068</v>
+        <v>-0.76</v>
       </c>
       <c r="J19">
-        <v>-10.66038995726496</v>
+        <v>-0.76</v>
       </c>
       <c r="K19">
-        <v>3.29</v>
+        <v>-0.073</v>
       </c>
       <c r="L19">
-        <v>28.11965811965812</v>
+        <v>-0.9733333333333333</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2776,7 +2746,7 @@
         <v>-0</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2785,79 +2755,64 @@
         <v>-0</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>0.001413427561837456</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>0.2860869565217392</v>
+        <v>0.3967391304347826</v>
       </c>
       <c r="X19">
-        <v>0.08941359964765429</v>
+        <v>0.07162925291611097</v>
       </c>
       <c r="Y19">
-        <v>0.1966733568740849</v>
-      </c>
-      <c r="Z19">
-        <v>0.01051969070311095</v>
-      </c>
-      <c r="AA19">
-        <v>-0.1121440051249775</v>
+        <v>0.3251098775186716</v>
       </c>
       <c r="AB19">
-        <v>0.08263976752374189</v>
-      </c>
-      <c r="AC19">
-        <v>-0.1947837726487194</v>
+        <v>0.06933412755888343</v>
       </c>
       <c r="AD19">
-        <v>1.44</v>
+        <v>0.243</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.44</v>
+        <v>0.243</v>
       </c>
       <c r="AG19">
-        <v>1.432</v>
+        <v>0.243</v>
       </c>
       <c r="AH19">
-        <v>0.2028169014084507</v>
+        <v>0.1103041307308216</v>
       </c>
       <c r="AI19">
-        <v>0.1018387553041018</v>
+        <v>-6.230769230769234</v>
       </c>
       <c r="AJ19">
-        <v>0.2019176536943034</v>
+        <v>0.1103041307308216</v>
       </c>
       <c r="AK19">
-        <v>0.1013303141805831</v>
+        <v>-6.230769230769234</v>
       </c>
       <c r="AL19">
-        <v>0.301</v>
+        <v>0.015</v>
       </c>
       <c r="AM19">
-        <v>0.278</v>
-      </c>
-      <c r="AN19">
-        <v>-2.054208273894436</v>
+        <v>0.015</v>
       </c>
       <c r="AO19">
-        <v>-4.152823920265781</v>
-      </c>
-      <c r="AP19">
-        <v>-2.042796005706134</v>
+        <v>-3.8</v>
       </c>
       <c r="AQ19">
-        <v>-4.496402877697842</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="20">
@@ -2868,7 +2823,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Soho Development S.A. (WSE:SHD)</t>
+          <t>Grupa Trinity S.A. (WSE:GTY)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2876,29 +2831,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D20">
-        <v>-0.552</v>
-      </c>
-      <c r="E20">
-        <v>0.0803</v>
-      </c>
-      <c r="G20">
-        <v>-3.165680473372781</v>
-      </c>
-      <c r="H20">
-        <v>-3.165680473372781</v>
-      </c>
-      <c r="I20">
-        <v>-2.331360946745562</v>
-      </c>
-      <c r="J20">
-        <v>-2.31803888419273</v>
-      </c>
       <c r="K20">
-        <v>2.44</v>
-      </c>
-      <c r="L20">
-        <v>7.218934911242603</v>
+        <v>-0.03</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2907,7 +2841,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2916,1245 +2850,64 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>3.15</v>
+        <v>0.002</v>
       </c>
       <c r="V20">
-        <v>1.105263157894737</v>
+        <v>0.003021148036253776</v>
       </c>
       <c r="W20">
-        <v>0.3771251931993818</v>
+        <v>0.3296703296703297</v>
       </c>
       <c r="X20">
-        <v>0.0810755564438615</v>
+        <v>0.07399922677683116</v>
       </c>
       <c r="Y20">
-        <v>0.2960496367555203</v>
-      </c>
-      <c r="Z20">
-        <v>0.05841686830279987</v>
-      </c>
-      <c r="AA20">
-        <v>-0.1354125722186559</v>
+        <v>0.2556711028934985</v>
       </c>
       <c r="AB20">
-        <v>0.0808489992385116</v>
-      </c>
-      <c r="AC20">
-        <v>-0.2162615714571675</v>
+        <v>0.06978779098967988</v>
       </c>
       <c r="AD20">
-        <v>0.026</v>
+        <v>0.147</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0.026</v>
+        <v>0.147</v>
       </c>
       <c r="AG20">
-        <v>-3.124</v>
+        <v>0.145</v>
       </c>
       <c r="AH20">
-        <v>0.009040333796940195</v>
+        <v>0.1817058096415327</v>
       </c>
       <c r="AI20">
-        <v>0.007250418293363078</v>
+        <v>10.50000000000001</v>
       </c>
       <c r="AJ20">
-        <v>11.4014598540146</v>
+        <v>0.1796778190830235</v>
       </c>
       <c r="AK20">
-        <v>-7.1651376146789</v>
+        <v>12.08333333333335</v>
       </c>
       <c r="AL20">
-        <v>0.014</v>
+        <v>0.006</v>
       </c>
       <c r="AM20">
-        <v>-0.003999999999999998</v>
-      </c>
-      <c r="AN20">
-        <v>-0.03341902313624678</v>
+        <v>0.006</v>
       </c>
       <c r="AO20">
-        <v>-56.28571428571428</v>
-      </c>
-      <c r="AP20">
-        <v>4.015424164524422</v>
+        <v>-3.833333333333333</v>
       </c>
       <c r="AQ20">
-        <v>197.0000000000001</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Skarbiec Holding S.A. (WSE:SKH)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>-0.0713</v>
-      </c>
-      <c r="G21">
-        <v>0.2462585034013606</v>
-      </c>
-      <c r="H21">
-        <v>0.2462585034013606</v>
-      </c>
-      <c r="I21">
-        <v>-0.04312925170068028</v>
-      </c>
-      <c r="J21">
-        <v>-0.04312925170068028</v>
-      </c>
-      <c r="K21">
-        <v>-1.38</v>
-      </c>
-      <c r="L21">
-        <v>-0.09387755102040816</v>
-      </c>
-      <c r="M21">
-        <v>-0</v>
-      </c>
-      <c r="N21">
-        <v>-0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>-0</v>
-      </c>
-      <c r="Q21">
-        <v>-0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>20.4</v>
-      </c>
-      <c r="V21">
-        <v>0.6891891891891891</v>
-      </c>
-      <c r="W21">
-        <v>-0.026953125</v>
-      </c>
-      <c r="X21">
-        <v>0.08148663582218676</v>
-      </c>
-      <c r="Y21">
-        <v>-0.1084397608221868</v>
-      </c>
-      <c r="Z21">
-        <v>3.213817227809359</v>
-      </c>
-      <c r="AA21">
-        <v>-0.1386095321381723</v>
-      </c>
-      <c r="AB21">
-        <v>0.08089350133623706</v>
-      </c>
-      <c r="AC21">
-        <v>-0.2195030334744094</v>
-      </c>
-      <c r="AD21">
-        <v>0.628</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0.628</v>
-      </c>
-      <c r="AG21">
-        <v>-19.772</v>
-      </c>
-      <c r="AH21">
-        <v>0.02077543998941379</v>
-      </c>
-      <c r="AI21">
-        <v>0.01557230708192819</v>
-      </c>
-      <c r="AJ21">
-        <v>-2.011803011803011</v>
-      </c>
-      <c r="AK21">
-        <v>-0.9921718185467681</v>
-      </c>
-      <c r="AL21">
-        <v>0.021</v>
-      </c>
-      <c r="AM21">
-        <v>-0.362</v>
-      </c>
-      <c r="AN21">
-        <v>-1.37719298245614</v>
-      </c>
-      <c r="AO21">
-        <v>-30.19047619047619</v>
-      </c>
-      <c r="AP21">
-        <v>43.35964912280701</v>
-      </c>
-      <c r="AQ21">
-        <v>1.751381215469613</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Open Finance S.A. (WSE:OPF)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>-0.342</v>
-      </c>
-      <c r="G22">
-        <v>-0.3392181588902901</v>
-      </c>
-      <c r="H22">
-        <v>-0.3392181588902901</v>
-      </c>
-      <c r="I22">
-        <v>-0.6191677175283733</v>
-      </c>
-      <c r="J22">
-        <v>-0.6191677175283733</v>
-      </c>
-      <c r="K22">
-        <v>-28.4</v>
-      </c>
-      <c r="L22">
-        <v>-3.581336696090794</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0.372</v>
-      </c>
-      <c r="V22">
-        <v>1.9375</v>
-      </c>
-      <c r="W22">
-        <v>-11.49797570850202</v>
-      </c>
-      <c r="X22">
-        <v>6.29493117132705</v>
-      </c>
-      <c r="Y22">
-        <v>-17.79290687982908</v>
-      </c>
-      <c r="Z22">
-        <v>0.2220293425915556</v>
-      </c>
-      <c r="AA22">
-        <v>-0.1374734012767387</v>
-      </c>
-      <c r="AB22">
-        <v>0.0990597900539176</v>
-      </c>
-      <c r="AC22">
-        <v>-0.2365331913306563</v>
-      </c>
-      <c r="AD22">
-        <v>35.1</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>35.1</v>
-      </c>
-      <c r="AG22">
-        <v>34.728</v>
-      </c>
-      <c r="AH22">
-        <v>0.9945596735804149</v>
-      </c>
-      <c r="AI22">
-        <v>4.178571428571428</v>
-      </c>
-      <c r="AJ22">
-        <v>0.9945017182130584</v>
-      </c>
-      <c r="AK22">
-        <v>4.325859491778774</v>
-      </c>
-      <c r="AL22">
-        <v>0.667</v>
-      </c>
-      <c r="AM22">
-        <v>0.666</v>
-      </c>
-      <c r="AN22">
-        <v>-8.032036613272311</v>
-      </c>
-      <c r="AO22">
-        <v>-7.361319340329834</v>
-      </c>
-      <c r="AP22">
-        <v>-7.946910755148742</v>
-      </c>
-      <c r="AQ22">
-        <v>-7.372372372372372</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>M.W. Trade SA (WSE:MWT)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>-0.524</v>
-      </c>
-      <c r="G23">
-        <v>-0.5964912280701754</v>
-      </c>
-      <c r="H23">
-        <v>-0.5964912280701754</v>
-      </c>
-      <c r="I23">
-        <v>-1.934210526315789</v>
-      </c>
-      <c r="J23">
-        <v>-1.934210526315789</v>
-      </c>
-      <c r="K23">
-        <v>-0.527</v>
-      </c>
-      <c r="L23">
-        <v>-2.31140350877193</v>
-      </c>
-      <c r="M23">
-        <v>5.94</v>
-      </c>
-      <c r="N23">
-        <v>2.302325581395349</v>
-      </c>
-      <c r="O23">
-        <v>-11.27134724857685</v>
-      </c>
-      <c r="P23">
-        <v>-0</v>
-      </c>
-      <c r="Q23">
-        <v>-0</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>5.94</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-      <c r="U23">
-        <v>4.53</v>
-      </c>
-      <c r="V23">
-        <v>1.755813953488372</v>
-      </c>
-      <c r="W23">
-        <v>-0.034</v>
-      </c>
-      <c r="X23">
-        <v>0.08267585791708221</v>
-      </c>
-      <c r="Y23">
-        <v>-0.1166758579170822</v>
-      </c>
-      <c r="Z23">
-        <v>0.08131241084165483</v>
-      </c>
-      <c r="AA23">
-        <v>-0.1572753209700429</v>
-      </c>
-      <c r="AB23">
-        <v>0.08125719846289658</v>
-      </c>
-      <c r="AC23">
-        <v>-0.2385325194329395</v>
-      </c>
-      <c r="AD23">
-        <v>0.145</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0.145</v>
-      </c>
-      <c r="AG23">
-        <v>-4.385000000000001</v>
-      </c>
-      <c r="AH23">
-        <v>0.05321100917431192</v>
-      </c>
-      <c r="AI23">
-        <v>0.02375102375102375</v>
-      </c>
-      <c r="AJ23">
-        <v>2.429362880886426</v>
-      </c>
-      <c r="AK23">
-        <v>-2.784126984126986</v>
-      </c>
-      <c r="AL23">
-        <v>0.118</v>
-      </c>
-      <c r="AM23">
-        <v>0.05399999999999999</v>
-      </c>
-      <c r="AN23">
-        <v>-0.3436018957345972</v>
-      </c>
-      <c r="AO23">
-        <v>-3.737288135593221</v>
-      </c>
-      <c r="AP23">
-        <v>10.39099526066351</v>
-      </c>
-      <c r="AQ23">
-        <v>-8.166666666666668</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SPARK VC S.A. (WSE:SPK)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K24">
-        <v>-0.027</v>
-      </c>
-      <c r="M24">
-        <v>0.048</v>
-      </c>
-      <c r="N24">
-        <v>0.0007339449541284404</v>
-      </c>
-      <c r="O24">
-        <v>-1.777777777777778</v>
-      </c>
-      <c r="P24">
-        <v>-0</v>
-      </c>
-      <c r="Q24">
-        <v>-0</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-      <c r="S24">
-        <v>0.048</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>0.001</v>
-      </c>
-      <c r="V24">
-        <v>1.529051987767584e-05</v>
-      </c>
-      <c r="W24">
-        <v>-0.2093023255813953</v>
-      </c>
-      <c r="X24">
-        <v>0.08077169089460928</v>
-      </c>
-      <c r="Y24">
-        <v>-0.2900740164760046</v>
-      </c>
-      <c r="Z24">
-        <v>0</v>
-      </c>
-      <c r="AA24">
-        <v>-0.1773049645390071</v>
-      </c>
-      <c r="AB24">
-        <v>0.08076714918724222</v>
-      </c>
-      <c r="AC24">
-        <v>-0.2580721137262493</v>
-      </c>
-      <c r="AD24">
-        <v>0.012</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0.012</v>
-      </c>
-      <c r="AG24">
-        <v>0.011</v>
-      </c>
-      <c r="AH24">
-        <v>0.000183452577508714</v>
-      </c>
-      <c r="AI24">
-        <v>0.09917355371900827</v>
-      </c>
-      <c r="AJ24">
-        <v>0.0001681674336120836</v>
-      </c>
-      <c r="AK24">
-        <v>0.09166666666666666</v>
-      </c>
-      <c r="AL24">
-        <v>0.001</v>
-      </c>
-      <c r="AM24">
-        <v>0.001</v>
-      </c>
-      <c r="AO24">
-        <v>-25</v>
-      </c>
-      <c r="AQ24">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Adiuvo Investments S.A. (WSE:ADV)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>-0.271</v>
-      </c>
-      <c r="G25">
-        <v>-10.46728971962617</v>
-      </c>
-      <c r="H25">
-        <v>-15.98130841121495</v>
-      </c>
-      <c r="I25">
-        <v>-4.672897196261682</v>
-      </c>
-      <c r="J25">
-        <v>-4.672897196261682</v>
-      </c>
-      <c r="K25">
-        <v>-1.78</v>
-      </c>
-      <c r="L25">
-        <v>-5.545171339563863</v>
-      </c>
-      <c r="M25">
-        <v>-0</v>
-      </c>
-      <c r="N25">
-        <v>-0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>-0</v>
-      </c>
-      <c r="Q25">
-        <v>-0</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
-      </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0.006</v>
-      </c>
-      <c r="V25">
-        <v>0.002678571428571428</v>
-      </c>
-      <c r="W25">
-        <v>-3.490196078431373</v>
-      </c>
-      <c r="X25">
-        <v>0.1945780127557292</v>
-      </c>
-      <c r="Y25">
-        <v>-3.684774091187102</v>
-      </c>
-      <c r="Z25">
-        <v>0.03721739130434783</v>
-      </c>
-      <c r="AA25">
-        <v>-0.1739130434782609</v>
-      </c>
-      <c r="AB25">
-        <v>0.08551140439918509</v>
-      </c>
-      <c r="AC25">
-        <v>-0.259424447877446</v>
-      </c>
-      <c r="AD25">
-        <v>7.5</v>
-      </c>
-      <c r="AE25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>7.5</v>
-      </c>
-      <c r="AG25">
-        <v>7.494</v>
-      </c>
-      <c r="AH25">
-        <v>0.7700205338809035</v>
-      </c>
-      <c r="AI25">
-        <v>1.070052789270937</v>
-      </c>
-      <c r="AJ25">
-        <v>0.7698787754263406</v>
-      </c>
-      <c r="AK25">
-        <v>1.07011280879623</v>
-      </c>
-      <c r="AL25">
-        <v>0.623</v>
-      </c>
-      <c r="AM25">
-        <v>0.591</v>
-      </c>
-      <c r="AN25">
-        <v>-5.244755244755245</v>
-      </c>
-      <c r="AO25">
-        <v>-2.407704654895666</v>
-      </c>
-      <c r="AP25">
-        <v>-5.240559440559441</v>
-      </c>
-      <c r="AQ25">
-        <v>-2.538071065989848</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Dr.Finance S.A. (WSE:DRF)</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>0.107</v>
-      </c>
-      <c r="G26">
-        <v>0.02487562189054727</v>
-      </c>
-      <c r="H26">
-        <v>0.02487562189054727</v>
-      </c>
-      <c r="I26">
-        <v>-0.01890547263681592</v>
-      </c>
-      <c r="J26">
-        <v>-0.01890547263681592</v>
-      </c>
-      <c r="K26">
-        <v>-0.046</v>
-      </c>
-      <c r="L26">
-        <v>-0.02288557213930349</v>
-      </c>
-      <c r="M26">
-        <v>0.001</v>
-      </c>
-      <c r="N26">
-        <v>0.001757469244288225</v>
-      </c>
-      <c r="O26">
-        <v>-0.02173913043478261</v>
-      </c>
-      <c r="P26">
-        <v>-0</v>
-      </c>
-      <c r="Q26">
-        <v>-0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0.001</v>
-      </c>
-      <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26">
-        <v>0.078</v>
-      </c>
-      <c r="V26">
-        <v>0.1370826010544816</v>
-      </c>
-      <c r="W26">
-        <v>-0.2100456621004566</v>
-      </c>
-      <c r="X26">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="Y26">
-        <v>-0.2908111159276163</v>
-      </c>
-      <c r="Z26">
-        <v>32.41935483870967</v>
-      </c>
-      <c r="AA26">
-        <v>-0.6129032258064516</v>
-      </c>
-      <c r="AB26">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="AC26">
-        <v>-0.6936686796336113</v>
-      </c>
-      <c r="AD26">
-        <v>0</v>
-      </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0</v>
-      </c>
-      <c r="AG26">
-        <v>-0.078</v>
-      </c>
-      <c r="AH26">
-        <v>0</v>
-      </c>
-      <c r="AI26">
-        <v>0</v>
-      </c>
-      <c r="AJ26">
-        <v>-0.1588594704684318</v>
-      </c>
-      <c r="AK26">
-        <v>-1.5</v>
-      </c>
-      <c r="AL26">
-        <v>0</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>-0</v>
-      </c>
-      <c r="AP26">
-        <v>2.108108108108108</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Metaversum S.A. (WSE:MET)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>0.199</v>
-      </c>
-      <c r="G27">
-        <v>0.5319148936170213</v>
-      </c>
-      <c r="H27">
-        <v>0.5319148936170213</v>
-      </c>
-      <c r="I27">
-        <v>-0.6808510638297872</v>
-      </c>
-      <c r="J27">
-        <v>-0.6808510638297872</v>
-      </c>
-      <c r="K27">
-        <v>-0.032</v>
-      </c>
-      <c r="L27">
-        <v>-0.6808510638297872</v>
-      </c>
-      <c r="M27">
-        <v>-0</v>
-      </c>
-      <c r="N27">
-        <v>-0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>-0</v>
-      </c>
-      <c r="Q27">
-        <v>-0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0.002</v>
-      </c>
-      <c r="V27">
-        <v>0.001785714285714286</v>
-      </c>
-      <c r="W27">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="X27">
-        <v>0.08197945445573115</v>
-      </c>
-      <c r="Y27">
-        <v>-5.415312787789064</v>
-      </c>
-      <c r="Z27">
-        <v>7.833333333333333</v>
-      </c>
-      <c r="AA27">
-        <v>-5.333333333333333</v>
-      </c>
-      <c r="AB27">
-        <v>0.08097798513093689</v>
-      </c>
-      <c r="AC27">
-        <v>-5.41431131846427</v>
-      </c>
-      <c r="AD27">
-        <v>0.04</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0.04</v>
-      </c>
-      <c r="AG27">
-        <v>0.038</v>
-      </c>
-      <c r="AH27">
-        <v>0.03448275862068965</v>
-      </c>
-      <c r="AI27">
-        <v>0.1834862385321101</v>
-      </c>
-      <c r="AJ27">
-        <v>0.03281519861830742</v>
-      </c>
-      <c r="AK27">
-        <v>0.1759259259259259</v>
-      </c>
-      <c r="AL27">
-        <v>0</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>-1.6</v>
-      </c>
-      <c r="AP27">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ABS Investment ASI SA (WSE:AIN)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K28">
-        <v>-0.638</v>
-      </c>
-      <c r="M28">
-        <v>-0</v>
-      </c>
-      <c r="N28">
-        <v>-0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>-0</v>
-      </c>
-      <c r="Q28">
-        <v>-0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0.074</v>
-      </c>
-      <c r="V28">
-        <v>0.04180790960451977</v>
-      </c>
-      <c r="X28">
-        <v>0.08376136046309191</v>
-      </c>
-      <c r="AB28">
-        <v>0.08126467065908485</v>
-      </c>
-      <c r="AD28">
-        <v>0.156</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0.156</v>
-      </c>
-      <c r="AG28">
-        <v>0.082</v>
-      </c>
-      <c r="AH28">
-        <v>0.0809968847352025</v>
-      </c>
-      <c r="AI28">
-        <v>0.05172413793103448</v>
-      </c>
-      <c r="AJ28">
-        <v>0.04427645788336933</v>
-      </c>
-      <c r="AK28">
-        <v>0.02787219578518015</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-0.024</v>
-      </c>
-      <c r="AQ28">
-        <v>5.458333333333333</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Grupa Trinity S.A. (WSE:GTY)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>-17</v>
-      </c>
-      <c r="J29">
-        <v>-17</v>
-      </c>
-      <c r="K29">
-        <v>-0.045</v>
-      </c>
-      <c r="L29">
-        <v>-45</v>
-      </c>
-      <c r="M29">
-        <v>-0</v>
-      </c>
-      <c r="N29">
-        <v>-0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>-0</v>
-      </c>
-      <c r="Q29">
-        <v>-0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0.001</v>
-      </c>
-      <c r="V29">
-        <v>0.0007936507936507937</v>
-      </c>
-      <c r="W29">
-        <v>0.7894736842105262</v>
-      </c>
-      <c r="X29">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="Y29">
-        <v>0.7087082303833665</v>
-      </c>
-      <c r="AB29">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>-0.001</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AI29">
-        <v>-0</v>
-      </c>
-      <c r="AJ29">
-        <v>-0.0007942811755361397</v>
-      </c>
-      <c r="AK29">
-        <v>0.0108695652173913</v>
-      </c>
-      <c r="AL29">
-        <v>0.004</v>
-      </c>
-      <c r="AM29">
-        <v>0.004</v>
-      </c>
-      <c r="AO29">
-        <v>-4.25</v>
-      </c>
-      <c r="AQ29">
-        <v>-4.25</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Baltic Bridge Spólka Akcyjna (WSE:WIS)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K30">
-        <v>-0.134</v>
-      </c>
-      <c r="M30">
-        <v>-0</v>
-      </c>
-      <c r="N30">
-        <v>-0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>-0</v>
-      </c>
-      <c r="Q30">
-        <v>-0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0.013</v>
-      </c>
-      <c r="V30">
-        <v>0.01192660550458715</v>
-      </c>
-      <c r="W30">
-        <v>0.161251504211793</v>
-      </c>
-      <c r="X30">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="Y30">
-        <v>0.0804860503846333</v>
-      </c>
-      <c r="AB30">
-        <v>0.08076545382715974</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>-0.013</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AI30">
-        <v>-0</v>
-      </c>
-      <c r="AJ30">
-        <v>-0.01207056638811513</v>
-      </c>
-      <c r="AK30">
-        <v>0.01591187270501836</v>
-      </c>
-      <c r="AL30">
-        <v>0.008</v>
-      </c>
-      <c r="AM30">
-        <v>0.008</v>
-      </c>
-      <c r="AN30">
-        <v>-0</v>
-      </c>
-      <c r="AO30">
-        <v>-11.875</v>
-      </c>
-      <c r="AP30">
-        <v>0.1368421052631579</v>
-      </c>
-      <c r="AQ30">
-        <v>-11.875</v>
+        <v>-3.833333333333333</v>
       </c>
     </row>
   </sheetData>
